--- a/4_pagos/efectivo/inputs/mesa_6.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\4_pagos\efectivo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6CA212-BB70-4516-8AB2-FB72F706A9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEADA9AE-31CC-481B-8DB6-1BE022A11807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>pago fraccionado</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
@@ -233,10 +230,13 @@
     <t>exonerado</t>
   </si>
   <si>
-    <t>pago fraccionado + exoneracion</t>
-  </si>
-  <si>
     <t>BLANCO</t>
+  </si>
+  <si>
+    <t>compromiso</t>
+  </si>
+  <si>
+    <t>compromiso + exoneracion</t>
   </si>
 </sst>
 </file>
@@ -352,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -375,6 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -688,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.81640625" customWidth="1"/>
@@ -701,20 +702,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="13"/>
+      <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
@@ -801,7 +802,7 @@
         <v>46178</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -864,7 +865,7 @@
         <v>46181</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>45</v>
@@ -879,7 +880,7 @@
         <v>46178</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -919,7 +920,7 @@
         <v>46181</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -937,7 +938,7 @@
         <v>46178</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1399,7 +1400,7 @@
         <v>46181</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -1451,7 +1452,7 @@
         <v>46181</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1634,7 +1635,30 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F36" s="7"/>
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36" s="7">
+        <v>8</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8">
+        <v>46179</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
@@ -1644,25 +1668,22 @@
         <v>46181</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F37" s="7">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37" s="8">
         <v>46179</v>
-      </c>
-      <c r="I37" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -1673,18 +1694,18 @@
         <v>46181</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>383</v>
       </c>
       <c r="F38" s="7">
-        <v>100</v>
-      </c>
-      <c r="G38">
+        <v>383</v>
+      </c>
+      <c r="G38" s="10">
         <v>0</v>
       </c>
       <c r="H38" s="8">
@@ -1699,16 +1720,16 @@
         <v>46181</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>383</v>
+        <v>70</v>
       </c>
       <c r="F39" s="7">
-        <v>383</v>
+        <v>70</v>
       </c>
       <c r="G39" s="10">
         <v>0</v>
@@ -1725,16 +1746,16 @@
         <v>46181</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F40" s="7">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G40" s="10">
         <v>0</v>
@@ -1751,22 +1772,25 @@
         <v>46181</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F41" s="7">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G41" s="10">
         <v>0</v>
       </c>
       <c r="H41" s="8">
         <v>46179</v>
+      </c>
+      <c r="I41" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -1780,22 +1804,19 @@
         <v>38</v>
       </c>
       <c r="D42">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F42" s="7">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G42" s="10">
         <v>0</v>
       </c>
       <c r="H42" s="8">
         <v>46179</v>
-      </c>
-      <c r="I42" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -1806,22 +1827,25 @@
         <v>46181</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="F43" s="7">
-        <v>49</v>
+        <v>208</v>
       </c>
       <c r="G43" s="10">
         <v>0</v>
       </c>
       <c r="H43" s="8">
         <v>46179</v>
+      </c>
+      <c r="I43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -1832,25 +1856,22 @@
         <v>46181</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>208</v>
+        <v>50</v>
       </c>
       <c r="F44" s="7">
-        <v>208</v>
+        <v>50</v>
       </c>
       <c r="G44" s="10">
         <v>0</v>
       </c>
       <c r="H44" s="8">
         <v>46179</v>
-      </c>
-      <c r="I44" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -1861,16 +1882,16 @@
         <v>46181</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D45">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F45" s="7">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="G45" s="10">
         <v>0</v>
@@ -1887,16 +1908,16 @@
         <v>46181</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F46" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G46" s="10">
         <v>0</v>
@@ -1913,16 +1934,16 @@
         <v>46181</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D47">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E47">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F47" s="7">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="G47" s="10">
         <v>0</v>
@@ -1939,16 +1960,16 @@
         <v>46181</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F48" s="7">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="G48" s="10">
         <v>0</v>
@@ -1965,16 +1986,16 @@
         <v>46181</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F49" s="7">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G49" s="10">
         <v>0</v>
@@ -1991,22 +2012,25 @@
         <v>46181</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F50" s="7">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G50" s="10">
         <v>0</v>
       </c>
       <c r="H50" s="8">
         <v>46179</v>
+      </c>
+      <c r="I50" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2017,25 +2041,22 @@
         <v>46181</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F51" s="7">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G51" s="10">
         <v>0</v>
       </c>
       <c r="H51" s="8">
         <v>46179</v>
-      </c>
-      <c r="I51" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2046,16 +2067,16 @@
         <v>46181</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="F52" s="7">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="G52" s="10">
         <v>0</v>
@@ -2072,16 +2093,16 @@
         <v>46181</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E53">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F53" s="7">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G53" s="10">
         <v>0</v>
@@ -2098,22 +2119,25 @@
         <v>46181</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E54">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F54" s="7">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G54" s="10">
         <v>0</v>
       </c>
       <c r="H54" s="8">
         <v>46179</v>
+      </c>
+      <c r="I54" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2124,16 +2148,16 @@
         <v>46181</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D55">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F55" s="7">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G55" s="10">
         <v>0</v>
@@ -2153,25 +2177,22 @@
         <v>46181</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D56">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E56">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F56" s="7">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="G56" s="10">
         <v>0</v>
       </c>
       <c r="H56" s="8">
         <v>46179</v>
-      </c>
-      <c r="I56" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2182,22 +2203,25 @@
         <v>46181</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="F57" s="7">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="G57" s="10">
         <v>0</v>
       </c>
       <c r="H57" s="8">
         <v>46179</v>
+      </c>
+      <c r="I57" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2208,25 +2232,22 @@
         <v>46181</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D58">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="F58" s="7">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G58" s="10">
         <v>0</v>
       </c>
       <c r="H58" s="8">
         <v>46179</v>
-      </c>
-      <c r="I58" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2237,16 +2258,16 @@
         <v>46181</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F59" s="7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G59" s="10">
         <v>0</v>
@@ -2263,22 +2284,25 @@
         <v>46181</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F60" s="7">
-        <v>50</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>52</v>
       </c>
       <c r="H60" s="8">
         <v>46179</v>
+      </c>
+      <c r="I60" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2289,25 +2313,22 @@
         <v>46181</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E61">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F61" s="7">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G61">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H61" s="8">
         <v>46179</v>
-      </c>
-      <c r="I61" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2318,18 +2339,18 @@
         <v>46181</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="D62" t="s">
+        <v>64</v>
       </c>
       <c r="E62">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="F62" s="7">
-        <v>61</v>
-      </c>
-      <c r="G62">
+        <v>107</v>
+      </c>
+      <c r="G62" s="10">
         <v>0</v>
       </c>
       <c r="H62" s="8">
@@ -2344,16 +2365,16 @@
         <v>46181</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E63">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F63" s="7">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G63" s="10">
         <v>0</v>
@@ -2370,16 +2391,16 @@
         <v>46181</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E64">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F64" s="7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G64" s="10">
         <v>0</v>
@@ -2396,16 +2417,16 @@
         <v>46181</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="F65" s="7">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="G65" s="10">
         <v>0</v>
@@ -2422,22 +2443,25 @@
         <v>46181</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E66">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F66" s="7">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G66" s="10">
         <v>0</v>
       </c>
       <c r="H66" s="8">
         <v>46179</v>
+      </c>
+      <c r="I66" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
@@ -2448,10 +2472,10 @@
         <v>46181</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E67">
         <v>33</v>
@@ -2465,61 +2489,81 @@
       <c r="H67" s="8">
         <v>46179</v>
       </c>
-      <c r="I67" t="s">
-        <v>54</v>
+      <c r="J67" s="9">
+        <f>SUM(E36:E67)</f>
+        <v>2367</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+      <c r="A68" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B68" s="8">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="C68" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F68" s="7">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G68" s="10">
         <v>0</v>
       </c>
       <c r="H68" s="8">
-        <v>46179</v>
-      </c>
-      <c r="J68" s="9">
-        <f>SUM(E37:E68)</f>
-        <v>2367</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="G69" s="10"/>
+      <c r="A69" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="8">
+        <v>46186</v>
+      </c>
+      <c r="C69" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69">
+        <v>12</v>
+      </c>
+      <c r="E69">
+        <v>177</v>
+      </c>
+      <c r="F69" s="7">
+        <v>177</v>
+      </c>
+      <c r="G69" s="10">
+        <v>0</v>
+      </c>
+      <c r="H69" s="8">
+        <v>46183</v>
+      </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B70" s="8">
-        <v>46185</v>
+        <v>46187</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E70">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F70" s="7">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G70" s="10">
         <v>0</v>
@@ -2533,19 +2577,19 @@
         <v>21</v>
       </c>
       <c r="B71" s="8">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="C71" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D71">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E71">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="F71" s="7">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="G71" s="10">
         <v>0</v>
@@ -2559,19 +2603,19 @@
         <v>21</v>
       </c>
       <c r="B72" s="8">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="C72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F72" s="7">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="G72" s="10">
         <v>0</v>
@@ -2579,25 +2623,28 @@
       <c r="H72" s="8">
         <v>46183</v>
       </c>
+      <c r="I72" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B73" s="8">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D73">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E73">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F73" s="7">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="G73" s="10">
         <v>0</v>
@@ -2605,25 +2652,28 @@
       <c r="H73" s="8">
         <v>46183</v>
       </c>
+      <c r="I73" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B74" s="8">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C74" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E74">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="F74" s="7">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="G74" s="10">
         <v>0</v>
@@ -2632,7 +2682,7 @@
         <v>46183</v>
       </c>
       <c r="I74" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
@@ -2640,19 +2690,19 @@
         <v>21</v>
       </c>
       <c r="B75" s="8">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="C75" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D75">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E75">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="F75" s="7">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="G75" s="10">
         <v>0</v>
@@ -2660,28 +2710,25 @@
       <c r="H75" s="8">
         <v>46183</v>
       </c>
-      <c r="I75" s="7" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B76" s="8">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="C76" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D76">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="F76" s="7">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="G76" s="10">
         <v>0</v>
@@ -2698,48 +2745,51 @@
         <v>21</v>
       </c>
       <c r="B77" s="8">
-        <v>46192</v>
+        <v>46194</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E77">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F77" s="7">
-        <v>59</v>
-      </c>
-      <c r="G77" s="10">
+        <v>86</v>
+      </c>
+      <c r="G77">
         <v>0</v>
       </c>
       <c r="H77" s="8">
         <v>46183</v>
       </c>
+      <c r="I77" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B78" s="8">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="C78" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E78">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F78" s="7">
-        <v>100</v>
-      </c>
-      <c r="G78" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>113</v>
       </c>
       <c r="H78" s="8">
         <v>46183</v>
@@ -2753,19 +2803,19 @@
         <v>21</v>
       </c>
       <c r="B79" s="8">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="C79" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D79">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E79">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F79" s="7">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -2773,31 +2823,28 @@
       <c r="H79" s="8">
         <v>46183</v>
       </c>
-      <c r="I79" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B80" s="8">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D80">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E80">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F80" s="7">
         <v>0</v>
       </c>
       <c r="G80">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H80" s="8">
         <v>46183</v>
@@ -2805,63 +2852,8 @@
       <c r="I80" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A81" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46196</v>
-      </c>
-      <c r="C81" t="s">
-        <v>62</v>
-      </c>
-      <c r="D81">
-        <v>15</v>
-      </c>
-      <c r="E81">
-        <v>32</v>
-      </c>
-      <c r="F81" s="7">
-        <v>32</v>
-      </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-      <c r="H81" s="8">
-        <v>46183</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A82" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82" s="8">
-        <v>46197</v>
-      </c>
-      <c r="C82" t="s">
-        <v>63</v>
-      </c>
-      <c r="D82">
-        <v>14</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" s="7">
-        <v>0</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82" s="8">
-        <v>46183</v>
-      </c>
-      <c r="I82" t="s">
-        <v>44</v>
-      </c>
-      <c r="J82" s="9">
-        <f>SUM(E70:E82)</f>
+      <c r="J80" s="9">
+        <f>SUM(E68:E80)</f>
         <v>1071</v>
       </c>
     </row>
@@ -2890,20 +2882,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="13"/>
+      <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2989,20 +2981,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="13"/>
+      <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>

--- a/4_pagos/efectivo/inputs/mesa_6.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_6.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\4_pagos\efectivo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEADA9AE-31CC-481B-8DB6-1BE022A11807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862580BE-1E3C-4BB4-B7FB-5734BBC91EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27660" yWindow="0" windowWidth="14610" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="registro_1" sheetId="1" r:id="rId1"/>
     <sheet name="registro_2" sheetId="2" r:id="rId2"/>
     <sheet name="registro_3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">registro_1!$A$2:$K$80</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="69">
   <si>
     <t>¿Quién cobró?</t>
   </si>
@@ -50,6 +53,9 @@
     <t>¿Alguna nota?</t>
   </si>
   <si>
+    <t>¿Qué tipo?</t>
+  </si>
+  <si>
     <t>COBRADOR</t>
   </si>
   <si>
@@ -77,6 +83,9 @@
     <t>COMENTARIO</t>
   </si>
   <si>
+    <t>CONCEPTO</t>
+  </si>
+  <si>
     <t>María García</t>
   </si>
   <si>
@@ -101,24 +110,42 @@
     <t>03/06/2026</t>
   </si>
   <si>
+    <t>tanque</t>
+  </si>
+  <si>
     <t>Wagner Trujillo</t>
   </si>
   <si>
     <t>P</t>
   </si>
   <si>
+    <t>compromiso + exoneracion</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
     <t>G</t>
   </si>
   <si>
+    <t>BLANCO</t>
+  </si>
+  <si>
+    <t>Hernestina Valladares?</t>
+  </si>
+  <si>
     <t>Q</t>
   </si>
   <si>
     <t>60?</t>
   </si>
   <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>Ocaña?</t>
+  </si>
+  <si>
     <t>16A</t>
   </si>
   <si>
@@ -128,6 +155,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>reclamo</t>
+  </si>
+  <si>
     <t>B1</t>
   </si>
   <si>
@@ -140,6 +170,9 @@
     <t>27A</t>
   </si>
   <si>
+    <t>K</t>
+  </si>
+  <si>
     <t>T</t>
   </si>
   <si>
@@ -155,6 +188,12 @@
     <t>C</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
@@ -170,18 +209,12 @@
     <t>U</t>
   </si>
   <si>
-    <t>reclamo</t>
-  </si>
-  <si>
-    <t>K</t>
+    <t>compromiso</t>
   </si>
   <si>
     <t>J</t>
   </si>
   <si>
-    <t>consumo +200 tanque</t>
-  </si>
-  <si>
     <t>F1</t>
   </si>
   <si>
@@ -194,6 +227,9 @@
     <t>G1</t>
   </si>
   <si>
+    <t>pago yape</t>
+  </si>
+  <si>
     <t>E</t>
   </si>
   <si>
@@ -203,47 +239,20 @@
     <t>C1</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Hernestina Valladares?</t>
-  </si>
-  <si>
-    <t>Ocaña?</t>
-  </si>
-  <si>
-    <t>pago yape</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
-    <t>H1</t>
+    <t>exonerado</t>
   </si>
   <si>
     <t>Z</t>
-  </si>
-  <si>
-    <t>exonerado</t>
-  </si>
-  <si>
-    <t>BLANCO</t>
-  </si>
-  <si>
-    <t>compromiso</t>
-  </si>
-  <si>
-    <t>compromiso + exoneracion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,8 +314,26 @@
       <color rgb="FF9CA3AF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF9A3412"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF9A3412"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF9CA3AF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,8 +366,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -348,11 +380,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -372,11 +419,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -689,102 +743,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K80"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="16" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12" style="9" customWidth="1"/>
+    <col min="6" max="6" width="16" style="9" customWidth="1"/>
+    <col min="7" max="8" width="14" style="9" customWidth="1"/>
+    <col min="9" max="9" width="30" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="15" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7">
         <v>46181</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>13</v>
@@ -792,28 +857,28 @@
       <c r="E4">
         <v>36</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4">
         <v>36</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>46178</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8">
+        <v>24</v>
+      </c>
+      <c r="B5" s="7">
         <v>46181</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -821,25 +886,25 @@
       <c r="E5">
         <v>34</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>34</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="8">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7">
         <v>46181</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -847,51 +912,51 @@
       <c r="E6">
         <v>34</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6">
         <v>34</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="8">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7">
         <v>46181</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>45</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>45</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>46178</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="8">
+        <v>24</v>
+      </c>
+      <c r="B8" s="7">
         <v>46181</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -899,28 +964,28 @@
       <c r="E8">
         <v>60</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8">
         <v>60</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>46178</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="8">
+        <v>24</v>
+      </c>
+      <c r="B9" s="7">
         <v>46181</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -928,54 +993,54 @@
       <c r="E9">
         <v>80</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9">
         <v>80</v>
       </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <v>46178</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="8">
+        <v>24</v>
+      </c>
+      <c r="B10" s="7">
         <v>46181</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>25</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10">
         <v>25</v>
       </c>
-      <c r="G10" s="10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="8">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7">
         <v>46181</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>11</v>
@@ -983,25 +1048,25 @@
       <c r="E11">
         <v>33</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
         <v>33</v>
       </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="8">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7">
         <v>46181</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1009,28 +1074,28 @@
       <c r="E12">
         <v>102</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12">
         <v>102</v>
       </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <v>46178</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="8">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7">
         <v>46181</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1038,25 +1103,25 @@
       <c r="E13">
         <v>71</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13">
         <v>71</v>
       </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="8">
+        <v>24</v>
+      </c>
+      <c r="B14" s="7">
         <v>46181</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1064,25 +1129,25 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14">
         <v>50</v>
       </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="8">
+        <v>24</v>
+      </c>
+      <c r="B15" s="7">
         <v>46181</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1090,54 +1155,54 @@
       <c r="E15">
         <v>20</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15">
         <v>20</v>
       </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <v>46178</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="8">
+        <v>24</v>
+      </c>
+      <c r="B16" s="7">
         <v>46181</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>28</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16">
         <v>28</v>
       </c>
-      <c r="G16" s="10">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="8">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7">
         <v>46181</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1145,28 +1210,28 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <v>46178</v>
       </c>
       <c r="I17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C18" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="8">
-        <v>46181</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
       </c>
       <c r="D18">
         <v>12</v>
@@ -1174,25 +1239,25 @@
       <c r="E18">
         <v>155</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
         <v>155</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="8">
+        <v>24</v>
+      </c>
+      <c r="B19" s="7">
         <v>46181</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>15</v>
@@ -1200,25 +1265,25 @@
       <c r="E19">
         <v>38</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19">
         <v>38</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="8">
+        <v>24</v>
+      </c>
+      <c r="B20" s="7">
         <v>46181</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1226,25 +1291,25 @@
       <c r="E20">
         <v>58</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20">
         <v>58</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="8">
+        <v>24</v>
+      </c>
+      <c r="B21" s="7">
         <v>46181</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -1252,25 +1317,25 @@
       <c r="E21">
         <v>53</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21">
         <v>53</v>
       </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8">
+        <v>24</v>
+      </c>
+      <c r="B22" s="7">
         <v>46181</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D22">
         <v>18</v>
@@ -1278,25 +1343,25 @@
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22">
         <v>36</v>
       </c>
-      <c r="G22" s="10">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="8">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7">
         <v>46181</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>20</v>
@@ -1304,25 +1369,25 @@
       <c r="E23">
         <v>110</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23">
         <v>110</v>
       </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="8">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7">
         <v>46181</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1330,25 +1395,25 @@
       <c r="E24">
         <v>28</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24">
         <v>28</v>
       </c>
-      <c r="G24" s="10">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="8">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7">
         <v>46181</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -1356,25 +1421,25 @@
       <c r="E25">
         <v>15</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25">
         <v>15</v>
       </c>
-      <c r="G25" s="10">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="8">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7">
         <v>46181</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>16</v>
@@ -1382,25 +1447,25 @@
       <c r="E26">
         <v>33</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26">
         <v>33</v>
       </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
-      <c r="H26" s="8">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="8">
+        <v>24</v>
+      </c>
+      <c r="B27" s="7">
         <v>46181</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -1408,25 +1473,25 @@
       <c r="E27">
         <v>8</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27">
         <v>8</v>
       </c>
-      <c r="G27" s="10">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="8">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7">
         <v>46181</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D28">
         <v>11</v>
@@ -1434,25 +1499,25 @@
       <c r="E28">
         <v>63</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28">
         <v>63</v>
       </c>
-      <c r="G28" s="10">
-        <v>0</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="8">
+        <v>24</v>
+      </c>
+      <c r="B29" s="7">
         <v>46181</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -1460,25 +1525,25 @@
       <c r="E29">
         <v>71</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
         <v>71</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="8">
+        <v>24</v>
+      </c>
+      <c r="B30" s="7">
         <v>46181</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D30">
         <v>17</v>
@@ -1486,25 +1551,25 @@
       <c r="E30">
         <v>121</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30">
         <v>121</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="8">
+        <v>24</v>
+      </c>
+      <c r="B31" s="7">
         <v>46181</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D31">
         <v>16</v>
@@ -1512,25 +1577,25 @@
       <c r="E31">
         <v>85</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
         <v>85</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="7">
         <v>46181</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -1538,25 +1603,25 @@
       <c r="E32">
         <v>33</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
         <v>33</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="8">
+        <v>24</v>
+      </c>
+      <c r="B33" s="7">
         <v>46181</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -1564,25 +1629,25 @@
       <c r="E33">
         <v>86</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
         <v>86</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="8">
+        <v>24</v>
+      </c>
+      <c r="B34" s="7">
         <v>46181</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1590,25 +1655,25 @@
       <c r="E34">
         <v>58</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34">
         <v>0</v>
       </c>
       <c r="G34">
         <v>58</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>46178</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="8">
+        <v>24</v>
+      </c>
+      <c r="B35" s="7">
         <v>46181</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1616,33 +1681,33 @@
       <c r="E35">
         <v>25</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35">
         <v>25</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <v>46178</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="8">
         <f>SUM(F4:F35)</f>
         <v>1206</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="8">
         <f>SUM(G4:G35)</f>
         <v>488</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" s="8">
+        <v>24</v>
+      </c>
+      <c r="B36" s="7">
         <v>46181</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1650,25 +1715,25 @@
       <c r="E36">
         <v>8</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36">
         <v>8</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="8">
+        <v>24</v>
+      </c>
+      <c r="B37" s="7">
         <v>46181</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>15</v>
@@ -1676,25 +1741,28 @@
       <c r="E37">
         <v>100</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37">
         <v>100</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="8">
+        <v>24</v>
+      </c>
+      <c r="B38" s="7">
         <v>46181</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -1702,25 +1770,25 @@
       <c r="E38">
         <v>383</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38">
         <v>383</v>
       </c>
-      <c r="G38" s="10">
-        <v>0</v>
-      </c>
-      <c r="H38" s="8">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="8">
+        <v>24</v>
+      </c>
+      <c r="B39" s="7">
         <v>46181</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D39">
         <v>14</v>
@@ -1728,25 +1796,28 @@
       <c r="E39">
         <v>70</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39">
         <v>70</v>
       </c>
-      <c r="G39" s="10">
-        <v>0</v>
-      </c>
-      <c r="H39" s="8">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="8">
+        <v>24</v>
+      </c>
+      <c r="B40" s="7">
         <v>46181</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1754,25 +1825,28 @@
       <c r="E40">
         <v>62</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40">
         <v>62</v>
       </c>
-      <c r="G40" s="10">
-        <v>0</v>
-      </c>
-      <c r="H40" s="8">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" s="8">
+        <v>24</v>
+      </c>
+      <c r="B41" s="7">
         <v>46181</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>26</v>
@@ -1780,28 +1854,28 @@
       <c r="E41">
         <v>58</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41">
         <v>58</v>
       </c>
-      <c r="G41" s="10">
-        <v>0</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7">
         <v>46179</v>
       </c>
       <c r="I41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" s="8">
+        <v>24</v>
+      </c>
+      <c r="B42" s="7">
         <v>46181</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D42">
         <v>27</v>
@@ -1809,54 +1883,51 @@
       <c r="E42">
         <v>49</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42">
         <v>49</v>
       </c>
-      <c r="G42" s="10">
-        <v>0</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7">
         <v>46179</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="8">
+        <v>24</v>
+      </c>
+      <c r="B43" s="7">
         <v>46181</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43">
-        <v>208</v>
-      </c>
-      <c r="F43" s="7">
-        <v>208</v>
-      </c>
-      <c r="G43" s="10">
-        <v>0</v>
-      </c>
-      <c r="H43" s="8">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
         <v>46179</v>
       </c>
-      <c r="I43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="8">
+        <v>24</v>
+      </c>
+      <c r="B44" s="7">
         <v>46181</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D44">
         <v>13</v>
@@ -1864,25 +1935,28 @@
       <c r="E44">
         <v>50</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44">
         <v>50</v>
       </c>
-      <c r="G44" s="10">
-        <v>0</v>
-      </c>
-      <c r="H44" s="8">
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45" s="8">
+        <v>24</v>
+      </c>
+      <c r="B45" s="7">
         <v>46181</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D45">
         <v>6</v>
@@ -1890,25 +1964,28 @@
       <c r="E45">
         <v>84</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45">
         <v>84</v>
       </c>
-      <c r="G45" s="10">
-        <v>0</v>
-      </c>
-      <c r="H45" s="8">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" s="8">
+        <v>24</v>
+      </c>
+      <c r="B46" s="7">
         <v>46181</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D46">
         <v>19</v>
@@ -1916,25 +1993,25 @@
       <c r="E46">
         <v>85</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46">
         <v>85</v>
       </c>
-      <c r="G46" s="10">
-        <v>0</v>
-      </c>
-      <c r="H46" s="8">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B47" s="8">
+        <v>24</v>
+      </c>
+      <c r="B47" s="7">
         <v>46181</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D47">
         <v>12</v>
@@ -1942,25 +2019,25 @@
       <c r="E47">
         <v>116</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47">
         <v>116</v>
       </c>
-      <c r="G47" s="10">
-        <v>0</v>
-      </c>
-      <c r="H47" s="8">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="8">
+        <v>24</v>
+      </c>
+      <c r="B48" s="7">
         <v>46181</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D48">
         <v>5</v>
@@ -1968,25 +2045,28 @@
       <c r="E48">
         <v>46</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48">
         <v>46</v>
       </c>
-      <c r="G48" s="10">
-        <v>0</v>
-      </c>
-      <c r="H48" s="8">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49" s="8">
+        <v>24</v>
+      </c>
+      <c r="B49" s="7">
         <v>46181</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1994,25 +2074,28 @@
       <c r="E49">
         <v>62</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49">
         <v>62</v>
       </c>
-      <c r="G49" s="10">
-        <v>0</v>
-      </c>
-      <c r="H49" s="8">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" s="8">
+        <v>24</v>
+      </c>
+      <c r="B50" s="7">
         <v>46181</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D50">
         <v>11</v>
@@ -2020,28 +2103,28 @@
       <c r="E50">
         <v>50</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50">
         <v>50</v>
       </c>
-      <c r="G50" s="10">
-        <v>0</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7">
         <v>46179</v>
       </c>
       <c r="I50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" s="8">
+        <v>24</v>
+      </c>
+      <c r="B51" s="7">
         <v>46181</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2049,25 +2132,25 @@
       <c r="E51">
         <v>61</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51">
         <v>61</v>
       </c>
-      <c r="G51" s="10">
-        <v>0</v>
-      </c>
-      <c r="H51" s="8">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>21</v>
-      </c>
-      <c r="B52" s="8">
+        <v>24</v>
+      </c>
+      <c r="B52" s="7">
         <v>46181</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D52">
         <v>5</v>
@@ -2075,25 +2158,28 @@
       <c r="E52">
         <v>14</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52">
         <v>14</v>
       </c>
-      <c r="G52" s="10">
-        <v>0</v>
-      </c>
-      <c r="H52" s="8">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="8">
+        <v>24</v>
+      </c>
+      <c r="B53" s="7">
         <v>46181</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D53">
         <v>14</v>
@@ -2101,25 +2187,28 @@
       <c r="E53">
         <v>58</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53">
         <v>58</v>
       </c>
-      <c r="G53" s="10">
-        <v>0</v>
-      </c>
-      <c r="H53" s="8">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B54" s="8">
+        <v>24</v>
+      </c>
+      <c r="B54" s="7">
         <v>46181</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D54">
         <v>13</v>
@@ -2127,28 +2216,28 @@
       <c r="E54">
         <v>35</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54">
         <v>35</v>
       </c>
-      <c r="G54" s="10">
-        <v>0</v>
-      </c>
-      <c r="H54" s="8">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7">
         <v>46179</v>
       </c>
       <c r="I54" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" s="8">
+        <v>24</v>
+      </c>
+      <c r="B55" s="7">
         <v>46181</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D55">
         <v>14</v>
@@ -2156,28 +2245,28 @@
       <c r="E55">
         <v>8</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55">
         <v>8</v>
       </c>
-      <c r="G55" s="10">
-        <v>0</v>
-      </c>
-      <c r="H55" s="8">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" s="7">
         <v>46179</v>
       </c>
       <c r="I55" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="8">
+        <v>24</v>
+      </c>
+      <c r="B56" s="7">
         <v>46181</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D56">
         <v>5</v>
@@ -2185,25 +2274,25 @@
       <c r="E56">
         <v>96</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56">
         <v>96</v>
       </c>
-      <c r="G56" s="10">
-        <v>0</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" s="8">
+        <v>24</v>
+      </c>
+      <c r="B57" s="7">
         <v>46181</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D57">
         <v>13</v>
@@ -2211,28 +2300,28 @@
       <c r="E57">
         <v>34</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57">
         <v>34</v>
       </c>
-      <c r="G57" s="10">
-        <v>0</v>
-      </c>
-      <c r="H57" s="8">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" s="7">
         <v>46179</v>
       </c>
       <c r="I57" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>21</v>
-      </c>
-      <c r="B58" s="8">
+        <v>24</v>
+      </c>
+      <c r="B58" s="7">
         <v>46181</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2240,25 +2329,25 @@
       <c r="E58">
         <v>55</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58">
         <v>55</v>
       </c>
-      <c r="G58" s="10">
-        <v>0</v>
-      </c>
-      <c r="H58" s="8">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>21</v>
-      </c>
-      <c r="B59" s="8">
+        <v>24</v>
+      </c>
+      <c r="B59" s="7">
         <v>46181</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D59">
         <v>5</v>
@@ -2266,25 +2355,28 @@
       <c r="E59">
         <v>50</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59">
         <v>50</v>
       </c>
-      <c r="G59" s="10">
-        <v>0</v>
-      </c>
-      <c r="H59" s="8">
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" s="7">
         <v>46179</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>21</v>
-      </c>
-      <c r="B60" s="8">
+        <v>24</v>
+      </c>
+      <c r="B60" s="7">
         <v>46181</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D60">
         <v>9</v>
@@ -2292,28 +2384,28 @@
       <c r="E60">
         <v>52</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60">
         <v>0</v>
       </c>
       <c r="G60">
         <v>52</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>46179</v>
       </c>
       <c r="I60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B61" s="8">
+        <v>24</v>
+      </c>
+      <c r="B61" s="7">
         <v>46181</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2321,51 +2413,51 @@
       <c r="E61">
         <v>61</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61">
         <v>61</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>21</v>
-      </c>
-      <c r="B62" s="8">
+        <v>24</v>
+      </c>
+      <c r="B62" s="7">
         <v>46181</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="D62" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="E62">
         <v>107</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62">
         <v>107</v>
       </c>
-      <c r="G62" s="10">
-        <v>0</v>
-      </c>
-      <c r="H62" s="8">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>21</v>
-      </c>
-      <c r="B63" s="8">
+        <v>24</v>
+      </c>
+      <c r="B63" s="7">
         <v>46181</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D63">
         <v>10</v>
@@ -2373,25 +2465,25 @@
       <c r="E63">
         <v>100</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63">
         <v>100</v>
       </c>
-      <c r="G63" s="10">
-        <v>0</v>
-      </c>
-      <c r="H63" s="8">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64" s="8">
+        <v>24</v>
+      </c>
+      <c r="B64" s="7">
         <v>46181</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D64">
         <v>5</v>
@@ -2399,25 +2491,25 @@
       <c r="E64">
         <v>95</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64">
         <v>95</v>
       </c>
-      <c r="G64" s="10">
-        <v>0</v>
-      </c>
-      <c r="H64" s="8">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65" s="8">
+        <v>24</v>
+      </c>
+      <c r="B65" s="7">
         <v>46181</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D65">
         <v>7</v>
@@ -2425,25 +2517,25 @@
       <c r="E65">
         <v>44</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65">
         <v>44</v>
       </c>
-      <c r="G65" s="10">
-        <v>0</v>
-      </c>
-      <c r="H65" s="8">
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" s="7">
         <v>46179</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>21</v>
-      </c>
-      <c r="B66" s="8">
+        <v>24</v>
+      </c>
+      <c r="B66" s="7">
         <v>46181</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D66">
         <v>10</v>
@@ -2451,28 +2543,28 @@
       <c r="E66">
         <v>33</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66">
         <v>33</v>
       </c>
-      <c r="G66" s="10">
-        <v>0</v>
-      </c>
-      <c r="H66" s="8">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" s="7">
         <v>46179</v>
       </c>
       <c r="I66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>21</v>
-      </c>
-      <c r="B67" s="8">
+        <v>24</v>
+      </c>
+      <c r="B67" s="7">
         <v>46181</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D67">
         <v>6</v>
@@ -2480,29 +2572,29 @@
       <c r="E67">
         <v>33</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67">
         <v>33</v>
       </c>
-      <c r="G67" s="10">
-        <v>0</v>
-      </c>
-      <c r="H67" s="8">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" s="7">
         <v>46179</v>
       </c>
-      <c r="J67" s="9">
+      <c r="J67" s="8">
         <f>SUM(E36:E67)</f>
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="8">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" s="7">
         <v>46185</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -2510,25 +2602,25 @@
       <c r="E68">
         <v>43</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68">
         <v>43</v>
       </c>
-      <c r="G68" s="10">
-        <v>0</v>
-      </c>
-      <c r="H68" s="8">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" s="8">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" s="7">
         <v>46186</v>
       </c>
       <c r="C69" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D69">
         <v>12</v>
@@ -2536,25 +2628,25 @@
       <c r="E69">
         <v>177</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69">
         <v>177</v>
       </c>
-      <c r="G69" s="10">
-        <v>0</v>
-      </c>
-      <c r="H69" s="8">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A70" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" s="8">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="7">
         <v>46187</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D70">
         <v>10</v>
@@ -2562,25 +2654,25 @@
       <c r="E70">
         <v>79</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70">
         <v>79</v>
       </c>
-      <c r="G70" s="10">
-        <v>0</v>
-      </c>
-      <c r="H70" s="8">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" s="8">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="7">
         <v>46188</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D71">
         <v>16</v>
@@ -2588,25 +2680,25 @@
       <c r="E71">
         <v>72</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71">
         <v>72</v>
       </c>
-      <c r="G71" s="10">
-        <v>0</v>
-      </c>
-      <c r="H71" s="8">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" s="8">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="7">
         <v>46189</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D72">
         <v>7</v>
@@ -2614,28 +2706,28 @@
       <c r="E72">
         <v>129</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72">
         <v>129</v>
       </c>
-      <c r="G72" s="10">
-        <v>0</v>
-      </c>
-      <c r="H72" s="8">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72" s="7">
         <v>46183</v>
       </c>
-      <c r="I72" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" s="8">
+      <c r="I72" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="7">
         <v>46190</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D73">
         <v>11</v>
@@ -2643,28 +2735,28 @@
       <c r="E73">
         <v>120</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73">
         <v>120</v>
       </c>
-      <c r="G73" s="10">
-        <v>0</v>
-      </c>
-      <c r="H73" s="8">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73" s="7">
         <v>46183</v>
       </c>
-      <c r="I73" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A74" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" s="8">
+      <c r="I73" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="7">
         <v>46191</v>
       </c>
       <c r="C74" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D74">
         <v>8</v>
@@ -2672,28 +2764,28 @@
       <c r="E74">
         <v>61</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74">
         <v>61</v>
       </c>
-      <c r="G74" s="10">
-        <v>0</v>
-      </c>
-      <c r="H74" s="8">
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" s="7">
         <v>46183</v>
       </c>
       <c r="I74" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A75" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" s="8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="7">
         <v>46192</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D75">
         <v>12</v>
@@ -2701,25 +2793,25 @@
       <c r="E75">
         <v>59</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75">
         <v>59</v>
       </c>
-      <c r="G75" s="10">
-        <v>0</v>
-      </c>
-      <c r="H75" s="8">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A76" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" s="8">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="7">
         <v>46193</v>
       </c>
       <c r="C76" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -2727,28 +2819,28 @@
       <c r="E76">
         <v>100</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76">
         <v>100</v>
       </c>
-      <c r="G76" s="10">
-        <v>0</v>
-      </c>
-      <c r="H76" s="8">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76" s="7">
         <v>46183</v>
       </c>
       <c r="I76" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A77" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" s="8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="7">
         <v>46194</v>
       </c>
       <c r="C77" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D77">
         <v>9</v>
@@ -2756,28 +2848,28 @@
       <c r="E77">
         <v>86</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77">
         <v>86</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="7">
         <v>46183</v>
       </c>
       <c r="I77" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A78" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="7">
         <v>46195</v>
       </c>
       <c r="C78" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D78">
         <v>39</v>
@@ -2785,28 +2877,28 @@
       <c r="E78">
         <v>113</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78">
         <v>0</v>
       </c>
       <c r="G78">
         <v>113</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="7">
         <v>46183</v>
       </c>
       <c r="I78" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A79" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" s="8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="7">
         <v>46196</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D79">
         <v>15</v>
@@ -2814,25 +2906,25 @@
       <c r="E79">
         <v>32</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79">
         <v>32</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="7">
         <v>46183</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A80" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" s="8">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="7">
         <v>46197</v>
       </c>
       <c r="C80" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D80">
         <v>14</v>
@@ -2840,24 +2932,54 @@
       <c r="E80">
         <v>0</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80">
         <v>0</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="7">
         <v>46183</v>
       </c>
       <c r="I80" t="s">
-        <v>44</v>
-      </c>
-      <c r="J80" s="9">
+        <v>38</v>
+      </c>
+      <c r="J80" s="8">
         <f>SUM(E68:E80)</f>
         <v>1071</v>
       </c>
     </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81">
+        <v>200</v>
+      </c>
+      <c r="F81">
+        <v>200</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A2:K80" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="A"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="A1:B1"/>
@@ -2869,92 +2991,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20" style="9" customWidth="1"/>
+    <col min="2" max="2" width="16" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12" style="9" customWidth="1"/>
+    <col min="6" max="6" width="16" style="9" customWidth="1"/>
+    <col min="7" max="8" width="14" style="9" customWidth="1"/>
+    <col min="9" max="9" width="30" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="15" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6"/>
+      <c r="J3" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2968,92 +3100,102 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20" style="9" customWidth="1"/>
+    <col min="2" max="2" width="16" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12" style="9" customWidth="1"/>
+    <col min="6" max="6" width="16" style="9" customWidth="1"/>
+    <col min="7" max="8" width="14" style="9" customWidth="1"/>
+    <col min="9" max="9" width="30" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="15" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6"/>
+      <c r="J3" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/4_pagos/efectivo/inputs/mesa_6.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_6.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,8 +93,20 @@
       <color rgb="009CA3AF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -126,8 +138,13 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -149,11 +166,55 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +248,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -566,6 +635,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -574,16 +644,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -592,6 +667,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -644,6 +724,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -697,6 +782,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -707,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -720,6 +810,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -728,16 +819,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -746,6 +842,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -798,6 +899,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -851,6 +957,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -861,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -874,6 +985,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -882,16 +994,21 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
+      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -900,6 +1017,11 @@
       <c r="J1" s="5" t="inlineStr">
         <is>
           <t>¿Qué tipo?</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
@@ -952,6 +1074,11 @@
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>CATEGORIA</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1132,11 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,otros"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/4_pagos/efectivo/inputs/mesa_6.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_6.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -256,6 +256,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -775,6 +778,1497 @@
       </c>
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -797,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -950,6 +2444,1497 @@
       </c>
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -972,7 +3957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1126,6 +4111,1497 @@
       <c r="I3" s="11" t="inlineStr"/>
       <c r="J3" s="11" t="inlineStr"/>
     </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="I4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="I5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="I6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="I7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="I8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="I9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="I10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="I11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="I12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="I13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="I14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="I15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="I16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="I17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="I18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="I19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="I20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="I21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="I22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="I23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="I24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="I26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="I27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="I28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="I29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="I30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="I31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="I33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="I35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="I36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="I37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="I38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="I39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="I40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="I41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="I42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="I48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="I49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="I50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="I51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="I53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="I54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="I55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="I56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="I57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="I58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="I59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="I60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="I61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="I62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="I63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="I64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="I65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="I66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="I67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="I68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="I69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="I70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="I71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="I72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="I73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="I74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="I75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="I76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="I77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="I78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="I79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="I80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="I81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="I82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="I83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="I84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="I85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="I86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="I87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="I88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="I89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="I90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="I91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="I92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="I93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="I94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="I95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="I96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="I97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="I98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="I99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="I100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="I101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="I102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="I103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="I104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="I105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="I106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="I107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="I108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="I109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="I110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="I111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="I112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="I113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="I114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="I115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="I116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="I117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="I118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="I119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="I120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="I121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="I122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="I123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="I124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="I125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="I126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="I127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="I128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="I129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="I130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="I131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="I132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="I133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="I134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="I135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="I136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="I137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="I138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="I139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="I140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="I141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="I142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="I143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="I144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="I145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="I146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="I147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="I148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="I149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="I150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="I151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="I152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="I153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="I154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="I155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="I156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="I157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="I158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="I159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="I160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="I161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="I162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="I163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="I164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="I165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="I166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="I167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="I168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="I169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="I170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="I171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="I172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="I173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="I174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="I175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="I176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="I177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="I178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="I179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="I180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="I181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="I182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="I183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="I184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="I185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="I186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="I187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="I188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="I189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="I190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="I191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="I192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="I193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="I194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="I195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="I196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="I197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="I198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="I199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="I200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="I201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="I202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="I203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="I204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="I205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="I206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="I207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="I208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="I209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="I210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="I211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="I212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="I213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="I214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="I215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="I216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="I217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="I218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="I219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="I220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="I221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="I222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="I223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="I224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="I225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="I226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="I227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="I228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="I229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="I230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="I231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="I232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="I233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="I234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="I235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="I236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="I237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="I238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="I239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="I240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="I241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="I242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="I243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="I244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="I245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="I246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="I247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="I248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="I249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="I250" s="16" t="n"/>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="I251" s="16" t="n"/>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="I252" s="16" t="n"/>
+    </row>
+    <row r="253" ht="18" customHeight="1">
+      <c r="I253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="I254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="I255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="18" customHeight="1">
+      <c r="I256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="I257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="18" customHeight="1">
+      <c r="I258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="18" customHeight="1">
+      <c r="I259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="I260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="I261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="18" customHeight="1">
+      <c r="I262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="18" customHeight="1">
+      <c r="I263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="18" customHeight="1">
+      <c r="I264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="I265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="I266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="I267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="18" customHeight="1">
+      <c r="I268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="I269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="I270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="18" customHeight="1">
+      <c r="I271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="18" customHeight="1">
+      <c r="I272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="18" customHeight="1">
+      <c r="I273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="I274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="18" customHeight="1">
+      <c r="I275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="18" customHeight="1">
+      <c r="I276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="18" customHeight="1">
+      <c r="I277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="18" customHeight="1">
+      <c r="I278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="18" customHeight="1">
+      <c r="I279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="18" customHeight="1">
+      <c r="I280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="18" customHeight="1">
+      <c r="I281" s="16" t="n"/>
+    </row>
+    <row r="282" ht="18" customHeight="1">
+      <c r="I282" s="16" t="n"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="I283" s="16" t="n"/>
+    </row>
+    <row r="284" ht="18" customHeight="1">
+      <c r="I284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="18" customHeight="1">
+      <c r="I285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="18" customHeight="1">
+      <c r="I286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="I287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="18" customHeight="1">
+      <c r="I288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="18" customHeight="1">
+      <c r="I289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="I290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="18" customHeight="1">
+      <c r="I291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="18" customHeight="1">
+      <c r="I292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="18" customHeight="1">
+      <c r="I293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="18" customHeight="1">
+      <c r="I294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="18" customHeight="1">
+      <c r="I295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="18" customHeight="1">
+      <c r="I296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="18" customHeight="1">
+      <c r="I297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="18" customHeight="1">
+      <c r="I298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="18" customHeight="1">
+      <c r="I299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="18" customHeight="1">
+      <c r="I300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="18" customHeight="1">
+      <c r="I301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="18" customHeight="1">
+      <c r="I302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="I303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="18" customHeight="1">
+      <c r="I304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="18" customHeight="1">
+      <c r="I305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="18" customHeight="1">
+      <c r="I306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="18" customHeight="1">
+      <c r="I307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="18" customHeight="1">
+      <c r="I308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="18" customHeight="1">
+      <c r="I309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="18" customHeight="1">
+      <c r="I310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="18" customHeight="1">
+      <c r="I311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="18" customHeight="1">
+      <c r="I312" s="16" t="n"/>
+    </row>
+    <row r="313" ht="18" customHeight="1">
+      <c r="I313" s="16" t="n"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="I314" s="16" t="n"/>
+    </row>
+    <row r="315" ht="18" customHeight="1">
+      <c r="I315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="18" customHeight="1">
+      <c r="I316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="18" customHeight="1">
+      <c r="I317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="18" customHeight="1">
+      <c r="I318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="18" customHeight="1">
+      <c r="I319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="18" customHeight="1">
+      <c r="I320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="18" customHeight="1">
+      <c r="I321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="18" customHeight="1">
+      <c r="I322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="18" customHeight="1">
+      <c r="I323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="18" customHeight="1">
+      <c r="I324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="I325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="18" customHeight="1">
+      <c r="I326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="18" customHeight="1">
+      <c r="I327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="18" customHeight="1">
+      <c r="I328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="18" customHeight="1">
+      <c r="I329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="18" customHeight="1">
+      <c r="I330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="18" customHeight="1">
+      <c r="I331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="18" customHeight="1">
+      <c r="I332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="18" customHeight="1">
+      <c r="I333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="I334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="18" customHeight="1">
+      <c r="I335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="18" customHeight="1">
+      <c r="I336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="I337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="18" customHeight="1">
+      <c r="I338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="18" customHeight="1">
+      <c r="I339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="18" customHeight="1">
+      <c r="I340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="18" customHeight="1">
+      <c r="I341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="18" customHeight="1">
+      <c r="I342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="18" customHeight="1">
+      <c r="I343" s="16" t="n"/>
+    </row>
+    <row r="344" ht="18" customHeight="1">
+      <c r="I344" s="16" t="n"/>
+    </row>
+    <row r="345" ht="18" customHeight="1">
+      <c r="I345" s="16" t="n"/>
+    </row>
+    <row r="346" ht="18" customHeight="1">
+      <c r="I346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="18" customHeight="1">
+      <c r="I347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="18" customHeight="1">
+      <c r="I348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="18" customHeight="1">
+      <c r="I349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="18" customHeight="1">
+      <c r="I350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="18" customHeight="1">
+      <c r="I351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="18" customHeight="1">
+      <c r="I352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="18" customHeight="1">
+      <c r="I353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="18" customHeight="1">
+      <c r="I354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="18" customHeight="1">
+      <c r="I355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="18" customHeight="1">
+      <c r="I356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="18" customHeight="1">
+      <c r="I357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="18" customHeight="1">
+      <c r="I358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="18" customHeight="1">
+      <c r="I359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="18" customHeight="1">
+      <c r="I360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="18" customHeight="1">
+      <c r="I361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="I362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="18" customHeight="1">
+      <c r="I363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="18" customHeight="1">
+      <c r="I364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="I365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="18" customHeight="1">
+      <c r="I366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="I367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="18" customHeight="1">
+      <c r="I368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="18" customHeight="1">
+      <c r="I369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="18" customHeight="1">
+      <c r="I370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="18" customHeight="1">
+      <c r="I371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="18" customHeight="1">
+      <c r="I372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="18" customHeight="1">
+      <c r="I373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="18" customHeight="1">
+      <c r="I374" s="16" t="n"/>
+    </row>
+    <row r="375" ht="18" customHeight="1">
+      <c r="I375" s="16" t="n"/>
+    </row>
+    <row r="376" ht="18" customHeight="1">
+      <c r="I376" s="16" t="n"/>
+    </row>
+    <row r="377" ht="18" customHeight="1">
+      <c r="I377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="18" customHeight="1">
+      <c r="I378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="18" customHeight="1">
+      <c r="I379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="18" customHeight="1">
+      <c r="I380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="I381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="18" customHeight="1">
+      <c r="I382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="18" customHeight="1">
+      <c r="I383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="18" customHeight="1">
+      <c r="I384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="18" customHeight="1">
+      <c r="I385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="I386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="18" customHeight="1">
+      <c r="I387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="18" customHeight="1">
+      <c r="I388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="18" customHeight="1">
+      <c r="I389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="18" customHeight="1">
+      <c r="I390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="18" customHeight="1">
+      <c r="I391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="18" customHeight="1">
+      <c r="I392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="18" customHeight="1">
+      <c r="I393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="I394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="18" customHeight="1">
+      <c r="I395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="18" customHeight="1">
+      <c r="I396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="18" customHeight="1">
+      <c r="I397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="18" customHeight="1">
+      <c r="I398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="18" customHeight="1">
+      <c r="I399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="I400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="I401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="18" customHeight="1">
+      <c r="I402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="18" customHeight="1">
+      <c r="I403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="18" customHeight="1">
+      <c r="I404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="18" customHeight="1">
+      <c r="I405" s="16" t="n"/>
+    </row>
+    <row r="406" ht="18" customHeight="1">
+      <c r="I406" s="16" t="n"/>
+    </row>
+    <row r="407" ht="18" customHeight="1">
+      <c r="I407" s="16" t="n"/>
+    </row>
+    <row r="408" ht="18" customHeight="1">
+      <c r="I408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="I409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="18" customHeight="1">
+      <c r="I410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="18" customHeight="1">
+      <c r="I411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="18" customHeight="1">
+      <c r="I412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="18" customHeight="1">
+      <c r="I413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="18" customHeight="1">
+      <c r="I414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="18" customHeight="1">
+      <c r="I415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="18" customHeight="1">
+      <c r="I416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="18" customHeight="1">
+      <c r="I417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="18" customHeight="1">
+      <c r="I418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="I419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="18" customHeight="1">
+      <c r="I420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="18" customHeight="1">
+      <c r="I421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="18" customHeight="1">
+      <c r="I422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="18" customHeight="1">
+      <c r="I423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="18" customHeight="1">
+      <c r="I424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="18" customHeight="1">
+      <c r="I425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="18" customHeight="1">
+      <c r="I426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="18" customHeight="1">
+      <c r="I427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="18" customHeight="1">
+      <c r="I428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="18" customHeight="1">
+      <c r="I429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="18" customHeight="1">
+      <c r="I430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="I431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="18" customHeight="1">
+      <c r="I432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="I433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="18" customHeight="1">
+      <c r="I434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="18" customHeight="1">
+      <c r="I435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="18" customHeight="1">
+      <c r="I436" s="16" t="n"/>
+    </row>
+    <row r="437" ht="18" customHeight="1">
+      <c r="I437" s="16" t="n"/>
+    </row>
+    <row r="438" ht="18" customHeight="1">
+      <c r="I438" s="16" t="n"/>
+    </row>
+    <row r="439" ht="18" customHeight="1">
+      <c r="I439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="18" customHeight="1">
+      <c r="I440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="18" customHeight="1">
+      <c r="I441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="18" customHeight="1">
+      <c r="I442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="I443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="I444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="I445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="I446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="I447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="I448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="I449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="I450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="I451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="I452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="I453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="I454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="I455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="I456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="I457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="I458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="I459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="I460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="I461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="18" customHeight="1">
+      <c r="I462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="18" customHeight="1">
+      <c r="I463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="18" customHeight="1">
+      <c r="I464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="18" customHeight="1">
+      <c r="I465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="18" customHeight="1">
+      <c r="I466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="I467" s="16" t="n"/>
+    </row>
+    <row r="468" ht="18" customHeight="1">
+      <c r="I468" s="16" t="n"/>
+    </row>
+    <row r="469" ht="18" customHeight="1">
+      <c r="I469" s="16" t="n"/>
+    </row>
+    <row r="470" ht="18" customHeight="1">
+      <c r="I470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="18" customHeight="1">
+      <c r="I471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="18" customHeight="1">
+      <c r="I472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="18" customHeight="1">
+      <c r="I473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="18" customHeight="1">
+      <c r="I474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="18" customHeight="1">
+      <c r="I475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="18" customHeight="1">
+      <c r="I476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="18" customHeight="1">
+      <c r="I477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="18" customHeight="1">
+      <c r="I478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="18" customHeight="1">
+      <c r="I479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="I480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="18" customHeight="1">
+      <c r="I481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="18" customHeight="1">
+      <c r="I482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="18" customHeight="1">
+      <c r="I483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="18" customHeight="1">
+      <c r="I484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="18" customHeight="1">
+      <c r="I485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="18" customHeight="1">
+      <c r="I486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="18" customHeight="1">
+      <c r="I487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="18" customHeight="1">
+      <c r="I488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="18" customHeight="1">
+      <c r="I489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="18" customHeight="1">
+      <c r="I490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="I491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="18" customHeight="1">
+      <c r="I492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="I493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="18" customHeight="1">
+      <c r="I494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="18" customHeight="1">
+      <c r="I495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="18" customHeight="1">
+      <c r="I496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="18" customHeight="1">
+      <c r="I497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="18" customHeight="1">
+      <c r="I498" s="16" t="n"/>
+    </row>
+    <row r="499" ht="18" customHeight="1">
+      <c r="I499" s="16" t="n"/>
+    </row>
+    <row r="500" ht="18" customHeight="1">
+      <c r="I500" s="16" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C1:D1"/>

--- a/4_pagos/efectivo/inputs/mesa_6.xlsx
+++ b/4_pagos/efectivo/inputs/mesa_6.xlsx
@@ -60,6 +60,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00880E4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001D4ED8"/>
       <sz val="10"/>
     </font>
@@ -89,20 +95,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="009CA3AF"/>
+      <b val="1"/>
+      <color rgb="00880E4F"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00880E4F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00880E4F"/>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -144,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,55 +166,11 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00FFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00FFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,31 +187,29 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -647,21 +601,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -672,1603 +621,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2277,8 +2227,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2313,21 +2263,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -2338,1603 +2283,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3943,8 +3889,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3979,21 +3925,16 @@
           <t>¿Quién cobró?</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
           <t>¿Dónde vive?</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿Cuánto y cuándo?</t>
         </is>
       </c>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="12" t="n"/>
       <c r="I1" s="4" t="inlineStr">
         <is>
           <t>¿Alguna nota?</t>
@@ -4004,1603 +3945,1604 @@
           <t>¿Qué tipo?</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>¿Qué pasó?</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>COBRADOR</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>FECHA_REGISTRO</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>MONTO</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>MONTO_EFECTIVO</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>MONTO_YAPE</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>COMENTARIO</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>CATEGORIA</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>8C</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="I4" s="16" t="n"/>
+      <c r="I4" s="14" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="I5" s="16" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="I6" s="16" t="n"/>
+      <c r="I6" s="14" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="I7" s="16" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="14" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="I9" s="16" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="I10" s="16" t="n"/>
+      <c r="I10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="I11" s="16" t="n"/>
+      <c r="I11" s="14" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="I12" s="16" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="I13" s="16" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="I14" s="16" t="n"/>
+      <c r="I14" s="14" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="I15" s="16" t="n"/>
+      <c r="I15" s="14" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="I16" s="16" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="I17" s="16" t="n"/>
+      <c r="I17" s="14" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="I18" s="16" t="n"/>
+      <c r="I18" s="14" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="I19" s="16" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="I20" s="16" t="n"/>
+      <c r="I20" s="14" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="I21" s="16" t="n"/>
+      <c r="I21" s="14" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="I22" s="16" t="n"/>
+      <c r="I22" s="14" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="I23" s="16" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="I24" s="16" t="n"/>
+      <c r="I24" s="14" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="I25" s="16" t="n"/>
+      <c r="I25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="I26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="I27" s="16" t="n"/>
+      <c r="I27" s="14" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="I28" s="16" t="n"/>
+      <c r="I28" s="14" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="I29" s="16" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="I30" s="16" t="n"/>
+      <c r="I30" s="14" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="I31" s="16" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="I32" s="16" t="n"/>
+      <c r="I32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="I33" s="16" t="n"/>
+      <c r="I33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="I34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="I35" s="16" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="I36" s="16" t="n"/>
+      <c r="I36" s="14" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="I37" s="16" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="I38" s="16" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="I39" s="16" t="n"/>
+      <c r="I39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="I40" s="16" t="n"/>
+      <c r="I40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="I41" s="16" t="n"/>
+      <c r="I41" s="14" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="I42" s="16" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="I43" s="16" t="n"/>
+      <c r="I43" s="14" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="I44" s="16" t="n"/>
+      <c r="I44" s="14" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="I45" s="16" t="n"/>
+      <c r="I45" s="14" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="I46" s="16" t="n"/>
+      <c r="I46" s="14" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="I47" s="16" t="n"/>
+      <c r="I47" s="14" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="I48" s="16" t="n"/>
+      <c r="I48" s="14" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="I49" s="16" t="n"/>
+      <c r="I49" s="14" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="I50" s="16" t="n"/>
+      <c r="I50" s="14" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="I51" s="16" t="n"/>
+      <c r="I51" s="14" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="I52" s="16" t="n"/>
+      <c r="I52" s="14" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="I53" s="16" t="n"/>
+      <c r="I53" s="14" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="I54" s="16" t="n"/>
+      <c r="I54" s="14" t="n"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="I55" s="16" t="n"/>
+      <c r="I55" s="14" t="n"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="I56" s="16" t="n"/>
+      <c r="I56" s="14" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="I57" s="16" t="n"/>
+      <c r="I57" s="14" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="I58" s="16" t="n"/>
+      <c r="I58" s="14" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="I59" s="16" t="n"/>
+      <c r="I59" s="14" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="I60" s="16" t="n"/>
+      <c r="I60" s="14" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="I61" s="16" t="n"/>
+      <c r="I61" s="14" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="I62" s="16" t="n"/>
+      <c r="I62" s="14" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="I63" s="16" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="I64" s="16" t="n"/>
+      <c r="I64" s="14" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="I65" s="16" t="n"/>
+      <c r="I65" s="14" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="I66" s="16" t="n"/>
+      <c r="I66" s="14" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="I67" s="16" t="n"/>
+      <c r="I67" s="14" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="I68" s="16" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="I69" s="16" t="n"/>
+      <c r="I69" s="14" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="I70" s="16" t="n"/>
+      <c r="I70" s="14" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="I71" s="16" t="n"/>
+      <c r="I71" s="14" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="I72" s="16" t="n"/>
+      <c r="I72" s="14" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="I73" s="16" t="n"/>
+      <c r="I73" s="14" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="I74" s="16" t="n"/>
+      <c r="I74" s="14" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="I75" s="16" t="n"/>
+      <c r="I75" s="14" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="I76" s="16" t="n"/>
+      <c r="I76" s="14" t="n"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="I77" s="16" t="n"/>
+      <c r="I77" s="14" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="I78" s="16" t="n"/>
+      <c r="I78" s="14" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="I79" s="16" t="n"/>
+      <c r="I79" s="14" t="n"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="I80" s="16" t="n"/>
+      <c r="I80" s="14" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="I81" s="16" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="I82" s="16" t="n"/>
+      <c r="I82" s="14" t="n"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="I83" s="16" t="n"/>
+      <c r="I83" s="14" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="I84" s="16" t="n"/>
+      <c r="I84" s="14" t="n"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="I85" s="16" t="n"/>
+      <c r="I85" s="14" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="I86" s="16" t="n"/>
+      <c r="I86" s="14" t="n"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="I87" s="16" t="n"/>
+      <c r="I87" s="14" t="n"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="I88" s="16" t="n"/>
+      <c r="I88" s="14" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="I89" s="16" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="I90" s="16" t="n"/>
+      <c r="I90" s="14" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="I91" s="16" t="n"/>
+      <c r="I91" s="14" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="I92" s="16" t="n"/>
+      <c r="I92" s="14" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="I93" s="16" t="n"/>
+      <c r="I93" s="14" t="n"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="I94" s="16" t="n"/>
+      <c r="I94" s="14" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="I95" s="16" t="n"/>
+      <c r="I95" s="14" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="I96" s="16" t="n"/>
+      <c r="I96" s="14" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="I97" s="16" t="n"/>
+      <c r="I97" s="14" t="n"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="14" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="I99" s="16" t="n"/>
+      <c r="I99" s="14" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="I100" s="16" t="n"/>
+      <c r="I100" s="14" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="I101" s="16" t="n"/>
+      <c r="I101" s="14" t="n"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="I102" s="16" t="n"/>
+      <c r="I102" s="14" t="n"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="I103" s="16" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="I104" s="16" t="n"/>
+      <c r="I104" s="14" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="I105" s="16" t="n"/>
+      <c r="I105" s="14" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="I106" s="16" t="n"/>
+      <c r="I106" s="14" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="I107" s="16" t="n"/>
+      <c r="I107" s="14" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="I108" s="16" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="I109" s="16" t="n"/>
+      <c r="I109" s="14" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="I110" s="16" t="n"/>
+      <c r="I110" s="14" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="I111" s="16" t="n"/>
+      <c r="I111" s="14" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="I112" s="16" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="I113" s="16" t="n"/>
+      <c r="I113" s="14" t="n"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="I114" s="16" t="n"/>
+      <c r="I114" s="14" t="n"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="I115" s="16" t="n"/>
+      <c r="I115" s="14" t="n"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="14" t="n"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="14" t="n"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="I119" s="16" t="n"/>
+      <c r="I119" s="14" t="n"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="I120" s="16" t="n"/>
+      <c r="I120" s="14" t="n"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="I121" s="16" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="I122" s="16" t="n"/>
+      <c r="I122" s="14" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="I123" s="16" t="n"/>
+      <c r="I123" s="14" t="n"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="I124" s="16" t="n"/>
+      <c r="I124" s="14" t="n"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="I125" s="16" t="n"/>
+      <c r="I125" s="14" t="n"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="I126" s="16" t="n"/>
+      <c r="I126" s="14" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="I127" s="16" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="I128" s="16" t="n"/>
+      <c r="I128" s="14" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="I129" s="16" t="n"/>
+      <c r="I129" s="14" t="n"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="I130" s="16" t="n"/>
+      <c r="I130" s="14" t="n"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="I131" s="16" t="n"/>
+      <c r="I131" s="14" t="n"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="I132" s="16" t="n"/>
+      <c r="I132" s="14" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="I133" s="16" t="n"/>
+      <c r="I133" s="14" t="n"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="I134" s="16" t="n"/>
+      <c r="I134" s="14" t="n"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="I135" s="16" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="I136" s="16" t="n"/>
+      <c r="I136" s="14" t="n"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="I137" s="16" t="n"/>
+      <c r="I137" s="14" t="n"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="I138" s="16" t="n"/>
+      <c r="I138" s="14" t="n"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="I139" s="16" t="n"/>
+      <c r="I139" s="14" t="n"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="I140" s="16" t="n"/>
+      <c r="I140" s="14" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="I141" s="16" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="I142" s="16" t="n"/>
+      <c r="I142" s="14" t="n"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="I143" s="16" t="n"/>
+      <c r="I143" s="14" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="I144" s="16" t="n"/>
+      <c r="I144" s="14" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="I145" s="16" t="n"/>
+      <c r="I145" s="14" t="n"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="I146" s="16" t="n"/>
+      <c r="I146" s="14" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="I147" s="16" t="n"/>
+      <c r="I147" s="14" t="n"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="I148" s="16" t="n"/>
+      <c r="I148" s="14" t="n"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="I149" s="16" t="n"/>
+      <c r="I149" s="14" t="n"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="I150" s="16" t="n"/>
+      <c r="I150" s="14" t="n"/>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="I151" s="16" t="n"/>
+      <c r="I151" s="14" t="n"/>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="I152" s="16" t="n"/>
+      <c r="I152" s="14" t="n"/>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="I153" s="16" t="n"/>
+      <c r="I153" s="14" t="n"/>
     </row>
     <row r="154" ht="18" customHeight="1">
-      <c r="I154" s="16" t="n"/>
+      <c r="I154" s="14" t="n"/>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="I155" s="16" t="n"/>
+      <c r="I155" s="14" t="n"/>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="14" t="n"/>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="14" t="n"/>
     </row>
     <row r="158" ht="18" customHeight="1">
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="14" t="n"/>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="I159" s="16" t="n"/>
+      <c r="I159" s="14" t="n"/>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="I160" s="16" t="n"/>
+      <c r="I160" s="14" t="n"/>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="I161" s="16" t="n"/>
+      <c r="I161" s="14" t="n"/>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="I162" s="16" t="n"/>
+      <c r="I162" s="14" t="n"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="I163" s="16" t="n"/>
+      <c r="I163" s="14" t="n"/>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="I164" s="16" t="n"/>
+      <c r="I164" s="14" t="n"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="I165" s="16" t="n"/>
+      <c r="I165" s="14" t="n"/>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="I166" s="16" t="n"/>
+      <c r="I166" s="14" t="n"/>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="14" t="n"/>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="I168" s="16" t="n"/>
+      <c r="I168" s="14" t="n"/>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="I169" s="16" t="n"/>
+      <c r="I169" s="14" t="n"/>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="I170" s="16" t="n"/>
+      <c r="I170" s="14" t="n"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="I171" s="16" t="n"/>
+      <c r="I171" s="14" t="n"/>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="I172" s="16" t="n"/>
+      <c r="I172" s="14" t="n"/>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="I173" s="16" t="n"/>
+      <c r="I173" s="14" t="n"/>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="I174" s="16" t="n"/>
+      <c r="I174" s="14" t="n"/>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="I175" s="16" t="n"/>
+      <c r="I175" s="14" t="n"/>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="I176" s="16" t="n"/>
+      <c r="I176" s="14" t="n"/>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="I177" s="16" t="n"/>
+      <c r="I177" s="14" t="n"/>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="14" t="n"/>
     </row>
     <row r="179" ht="18" customHeight="1">
-      <c r="I179" s="16" t="n"/>
+      <c r="I179" s="14" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="I180" s="16" t="n"/>
+      <c r="I180" s="14" t="n"/>
     </row>
     <row r="181" ht="18" customHeight="1">
-      <c r="I181" s="16" t="n"/>
+      <c r="I181" s="14" t="n"/>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="14" t="n"/>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="I183" s="16" t="n"/>
+      <c r="I183" s="14" t="n"/>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="I184" s="16" t="n"/>
+      <c r="I184" s="14" t="n"/>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="I185" s="16" t="n"/>
+      <c r="I185" s="14" t="n"/>
     </row>
     <row r="186" ht="18" customHeight="1">
-      <c r="I186" s="16" t="n"/>
+      <c r="I186" s="14" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1">
-      <c r="I187" s="16" t="n"/>
+      <c r="I187" s="14" t="n"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="I188" s="16" t="n"/>
+      <c r="I188" s="14" t="n"/>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="I189" s="16" t="n"/>
+      <c r="I189" s="14" t="n"/>
     </row>
     <row r="190" ht="18" customHeight="1">
-      <c r="I190" s="16" t="n"/>
+      <c r="I190" s="14" t="n"/>
     </row>
     <row r="191" ht="18" customHeight="1">
-      <c r="I191" s="16" t="n"/>
+      <c r="I191" s="14" t="n"/>
     </row>
     <row r="192" ht="18" customHeight="1">
-      <c r="I192" s="16" t="n"/>
+      <c r="I192" s="14" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
-      <c r="I193" s="16" t="n"/>
+      <c r="I193" s="14" t="n"/>
     </row>
     <row r="194" ht="18" customHeight="1">
-      <c r="I194" s="16" t="n"/>
+      <c r="I194" s="14" t="n"/>
     </row>
     <row r="195" ht="18" customHeight="1">
-      <c r="I195" s="16" t="n"/>
+      <c r="I195" s="14" t="n"/>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="I196" s="16" t="n"/>
+      <c r="I196" s="14" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
-      <c r="I197" s="16" t="n"/>
+      <c r="I197" s="14" t="n"/>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="I198" s="16" t="n"/>
+      <c r="I198" s="14" t="n"/>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="I199" s="16" t="n"/>
+      <c r="I199" s="14" t="n"/>
     </row>
     <row r="200" ht="18" customHeight="1">
-      <c r="I200" s="16" t="n"/>
+      <c r="I200" s="14" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
-      <c r="I201" s="16" t="n"/>
+      <c r="I201" s="14" t="n"/>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="I202" s="16" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="I203" s="16" t="n"/>
+      <c r="I203" s="14" t="n"/>
     </row>
     <row r="204" ht="18" customHeight="1">
-      <c r="I204" s="16" t="n"/>
+      <c r="I204" s="14" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="I205" s="16" t="n"/>
+      <c r="I205" s="14" t="n"/>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="I206" s="16" t="n"/>
+      <c r="I206" s="14" t="n"/>
     </row>
     <row r="207" ht="18" customHeight="1">
-      <c r="I207" s="16" t="n"/>
+      <c r="I207" s="14" t="n"/>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="I208" s="16" t="n"/>
+      <c r="I208" s="14" t="n"/>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="I209" s="16" t="n"/>
+      <c r="I209" s="14" t="n"/>
     </row>
     <row r="210" ht="18" customHeight="1">
-      <c r="I210" s="16" t="n"/>
+      <c r="I210" s="14" t="n"/>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="I211" s="16" t="n"/>
+      <c r="I211" s="14" t="n"/>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="I212" s="16" t="n"/>
+      <c r="I212" s="14" t="n"/>
     </row>
     <row r="213" ht="18" customHeight="1">
-      <c r="I213" s="16" t="n"/>
+      <c r="I213" s="14" t="n"/>
     </row>
     <row r="214" ht="18" customHeight="1">
-      <c r="I214" s="16" t="n"/>
+      <c r="I214" s="14" t="n"/>
     </row>
     <row r="215" ht="18" customHeight="1">
-      <c r="I215" s="16" t="n"/>
+      <c r="I215" s="14" t="n"/>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="I216" s="16" t="n"/>
+      <c r="I216" s="14" t="n"/>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="I217" s="16" t="n"/>
+      <c r="I217" s="14" t="n"/>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="I218" s="16" t="n"/>
+      <c r="I218" s="14" t="n"/>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="I219" s="16" t="n"/>
+      <c r="I219" s="14" t="n"/>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="I220" s="16" t="n"/>
+      <c r="I220" s="14" t="n"/>
     </row>
     <row r="221" ht="18" customHeight="1">
-      <c r="I221" s="16" t="n"/>
+      <c r="I221" s="14" t="n"/>
     </row>
     <row r="222" ht="18" customHeight="1">
-      <c r="I222" s="16" t="n"/>
+      <c r="I222" s="14" t="n"/>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="I223" s="16" t="n"/>
+      <c r="I223" s="14" t="n"/>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="I224" s="16" t="n"/>
+      <c r="I224" s="14" t="n"/>
     </row>
     <row r="225" ht="18" customHeight="1">
-      <c r="I225" s="16" t="n"/>
+      <c r="I225" s="14" t="n"/>
     </row>
     <row r="226" ht="18" customHeight="1">
-      <c r="I226" s="16" t="n"/>
+      <c r="I226" s="14" t="n"/>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="I227" s="16" t="n"/>
+      <c r="I227" s="14" t="n"/>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="I228" s="16" t="n"/>
+      <c r="I228" s="14" t="n"/>
     </row>
     <row r="229" ht="18" customHeight="1">
-      <c r="I229" s="16" t="n"/>
+      <c r="I229" s="14" t="n"/>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="I230" s="16" t="n"/>
+      <c r="I230" s="14" t="n"/>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="I231" s="16" t="n"/>
+      <c r="I231" s="14" t="n"/>
     </row>
     <row r="232" ht="18" customHeight="1">
-      <c r="I232" s="16" t="n"/>
+      <c r="I232" s="14" t="n"/>
     </row>
     <row r="233" ht="18" customHeight="1">
-      <c r="I233" s="16" t="n"/>
+      <c r="I233" s="14" t="n"/>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="I234" s="16" t="n"/>
+      <c r="I234" s="14" t="n"/>
     </row>
     <row r="235" ht="18" customHeight="1">
-      <c r="I235" s="16" t="n"/>
+      <c r="I235" s="14" t="n"/>
     </row>
     <row r="236" ht="18" customHeight="1">
-      <c r="I236" s="16" t="n"/>
+      <c r="I236" s="14" t="n"/>
     </row>
     <row r="237" ht="18" customHeight="1">
-      <c r="I237" s="16" t="n"/>
+      <c r="I237" s="14" t="n"/>
     </row>
     <row r="238" ht="18" customHeight="1">
-      <c r="I238" s="16" t="n"/>
+      <c r="I238" s="14" t="n"/>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="I239" s="16" t="n"/>
+      <c r="I239" s="14" t="n"/>
     </row>
     <row r="240" ht="18" customHeight="1">
-      <c r="I240" s="16" t="n"/>
+      <c r="I240" s="14" t="n"/>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="I241" s="16" t="n"/>
+      <c r="I241" s="14" t="n"/>
     </row>
     <row r="242" ht="18" customHeight="1">
-      <c r="I242" s="16" t="n"/>
+      <c r="I242" s="14" t="n"/>
     </row>
     <row r="243" ht="18" customHeight="1">
-      <c r="I243" s="16" t="n"/>
+      <c r="I243" s="14" t="n"/>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="I244" s="16" t="n"/>
+      <c r="I244" s="14" t="n"/>
     </row>
     <row r="245" ht="18" customHeight="1">
-      <c r="I245" s="16" t="n"/>
+      <c r="I245" s="14" t="n"/>
     </row>
     <row r="246" ht="18" customHeight="1">
-      <c r="I246" s="16" t="n"/>
+      <c r="I246" s="14" t="n"/>
     </row>
     <row r="247" ht="18" customHeight="1">
-      <c r="I247" s="16" t="n"/>
+      <c r="I247" s="14" t="n"/>
     </row>
     <row r="248" ht="18" customHeight="1">
-      <c r="I248" s="16" t="n"/>
+      <c r="I248" s="14" t="n"/>
     </row>
     <row r="249" ht="18" customHeight="1">
-      <c r="I249" s="16" t="n"/>
+      <c r="I249" s="14" t="n"/>
     </row>
     <row r="250" ht="18" customHeight="1">
-      <c r="I250" s="16" t="n"/>
+      <c r="I250" s="14" t="n"/>
     </row>
     <row r="251" ht="18" customHeight="1">
-      <c r="I251" s="16" t="n"/>
+      <c r="I251" s="14" t="n"/>
     </row>
     <row r="252" ht="18" customHeight="1">
-      <c r="I252" s="16" t="n"/>
+      <c r="I252" s="14" t="n"/>
     </row>
     <row r="253" ht="18" customHeight="1">
-      <c r="I253" s="16" t="n"/>
+      <c r="I253" s="14" t="n"/>
     </row>
     <row r="254" ht="18" customHeight="1">
-      <c r="I254" s="16" t="n"/>
+      <c r="I254" s="14" t="n"/>
     </row>
     <row r="255" ht="18" customHeight="1">
-      <c r="I255" s="16" t="n"/>
+      <c r="I255" s="14" t="n"/>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="I256" s="16" t="n"/>
+      <c r="I256" s="14" t="n"/>
     </row>
     <row r="257" ht="18" customHeight="1">
-      <c r="I257" s="16" t="n"/>
+      <c r="I257" s="14" t="n"/>
     </row>
     <row r="258" ht="18" customHeight="1">
-      <c r="I258" s="16" t="n"/>
+      <c r="I258" s="14" t="n"/>
     </row>
     <row r="259" ht="18" customHeight="1">
-      <c r="I259" s="16" t="n"/>
+      <c r="I259" s="14" t="n"/>
     </row>
     <row r="260" ht="18" customHeight="1">
-      <c r="I260" s="16" t="n"/>
+      <c r="I260" s="14" t="n"/>
     </row>
     <row r="261" ht="18" customHeight="1">
-      <c r="I261" s="16" t="n"/>
+      <c r="I261" s="14" t="n"/>
     </row>
     <row r="262" ht="18" customHeight="1">
-      <c r="I262" s="16" t="n"/>
+      <c r="I262" s="14" t="n"/>
     </row>
     <row r="263" ht="18" customHeight="1">
-      <c r="I263" s="16" t="n"/>
+      <c r="I263" s="14" t="n"/>
     </row>
     <row r="264" ht="18" customHeight="1">
-      <c r="I264" s="16" t="n"/>
+      <c r="I264" s="14" t="n"/>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="I265" s="16" t="n"/>
+      <c r="I265" s="14" t="n"/>
     </row>
     <row r="266" ht="18" customHeight="1">
-      <c r="I266" s="16" t="n"/>
+      <c r="I266" s="14" t="n"/>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="I267" s="16" t="n"/>
+      <c r="I267" s="14" t="n"/>
     </row>
     <row r="268" ht="18" customHeight="1">
-      <c r="I268" s="16" t="n"/>
+      <c r="I268" s="14" t="n"/>
     </row>
     <row r="269" ht="18" customHeight="1">
-      <c r="I269" s="16" t="n"/>
+      <c r="I269" s="14" t="n"/>
     </row>
     <row r="270" ht="18" customHeight="1">
-      <c r="I270" s="16" t="n"/>
+      <c r="I270" s="14" t="n"/>
     </row>
     <row r="271" ht="18" customHeight="1">
-      <c r="I271" s="16" t="n"/>
+      <c r="I271" s="14" t="n"/>
     </row>
     <row r="272" ht="18" customHeight="1">
-      <c r="I272" s="16" t="n"/>
+      <c r="I272" s="14" t="n"/>
     </row>
     <row r="273" ht="18" customHeight="1">
-      <c r="I273" s="16" t="n"/>
+      <c r="I273" s="14" t="n"/>
     </row>
     <row r="274" ht="18" customHeight="1">
-      <c r="I274" s="16" t="n"/>
+      <c r="I274" s="14" t="n"/>
     </row>
     <row r="275" ht="18" customHeight="1">
-      <c r="I275" s="16" t="n"/>
+      <c r="I275" s="14" t="n"/>
     </row>
     <row r="276" ht="18" customHeight="1">
-      <c r="I276" s="16" t="n"/>
+      <c r="I276" s="14" t="n"/>
     </row>
     <row r="277" ht="18" customHeight="1">
-      <c r="I277" s="16" t="n"/>
+      <c r="I277" s="14" t="n"/>
     </row>
     <row r="278" ht="18" customHeight="1">
-      <c r="I278" s="16" t="n"/>
+      <c r="I278" s="14" t="n"/>
     </row>
     <row r="279" ht="18" customHeight="1">
-      <c r="I279" s="16" t="n"/>
+      <c r="I279" s="14" t="n"/>
     </row>
     <row r="280" ht="18" customHeight="1">
-      <c r="I280" s="16" t="n"/>
+      <c r="I280" s="14" t="n"/>
     </row>
     <row r="281" ht="18" customHeight="1">
-      <c r="I281" s="16" t="n"/>
+      <c r="I281" s="14" t="n"/>
     </row>
     <row r="282" ht="18" customHeight="1">
-      <c r="I282" s="16" t="n"/>
+      <c r="I282" s="14" t="n"/>
     </row>
     <row r="283" ht="18" customHeight="1">
-      <c r="I283" s="16" t="n"/>
+      <c r="I283" s="14" t="n"/>
     </row>
     <row r="284" ht="18" customHeight="1">
-      <c r="I284" s="16" t="n"/>
+      <c r="I284" s="14" t="n"/>
     </row>
     <row r="285" ht="18" customHeight="1">
-      <c r="I285" s="16" t="n"/>
+      <c r="I285" s="14" t="n"/>
     </row>
     <row r="286" ht="18" customHeight="1">
-      <c r="I286" s="16" t="n"/>
+      <c r="I286" s="14" t="n"/>
     </row>
     <row r="287" ht="18" customHeight="1">
-      <c r="I287" s="16" t="n"/>
+      <c r="I287" s="14" t="n"/>
     </row>
     <row r="288" ht="18" customHeight="1">
-      <c r="I288" s="16" t="n"/>
+      <c r="I288" s="14" t="n"/>
     </row>
     <row r="289" ht="18" customHeight="1">
-      <c r="I289" s="16" t="n"/>
+      <c r="I289" s="14" t="n"/>
     </row>
     <row r="290" ht="18" customHeight="1">
-      <c r="I290" s="16" t="n"/>
+      <c r="I290" s="14" t="n"/>
     </row>
     <row r="291" ht="18" customHeight="1">
-      <c r="I291" s="16" t="n"/>
+      <c r="I291" s="14" t="n"/>
     </row>
     <row r="292" ht="18" customHeight="1">
-      <c r="I292" s="16" t="n"/>
+      <c r="I292" s="14" t="n"/>
     </row>
     <row r="293" ht="18" customHeight="1">
-      <c r="I293" s="16" t="n"/>
+      <c r="I293" s="14" t="n"/>
     </row>
     <row r="294" ht="18" customHeight="1">
-      <c r="I294" s="16" t="n"/>
+      <c r="I294" s="14" t="n"/>
     </row>
     <row r="295" ht="18" customHeight="1">
-      <c r="I295" s="16" t="n"/>
+      <c r="I295" s="14" t="n"/>
     </row>
     <row r="296" ht="18" customHeight="1">
-      <c r="I296" s="16" t="n"/>
+      <c r="I296" s="14" t="n"/>
     </row>
     <row r="297" ht="18" customHeight="1">
-      <c r="I297" s="16" t="n"/>
+      <c r="I297" s="14" t="n"/>
     </row>
     <row r="298" ht="18" customHeight="1">
-      <c r="I298" s="16" t="n"/>
+      <c r="I298" s="14" t="n"/>
     </row>
     <row r="299" ht="18" customHeight="1">
-      <c r="I299" s="16" t="n"/>
+      <c r="I299" s="14" t="n"/>
     </row>
     <row r="300" ht="18" customHeight="1">
-      <c r="I300" s="16" t="n"/>
+      <c r="I300" s="14" t="n"/>
     </row>
     <row r="301" ht="18" customHeight="1">
-      <c r="I301" s="16" t="n"/>
+      <c r="I301" s="14" t="n"/>
     </row>
     <row r="302" ht="18" customHeight="1">
-      <c r="I302" s="16" t="n"/>
+      <c r="I302" s="14" t="n"/>
     </row>
     <row r="303" ht="18" customHeight="1">
-      <c r="I303" s="16" t="n"/>
+      <c r="I303" s="14" t="n"/>
     </row>
     <row r="304" ht="18" customHeight="1">
-      <c r="I304" s="16" t="n"/>
+      <c r="I304" s="14" t="n"/>
     </row>
     <row r="305" ht="18" customHeight="1">
-      <c r="I305" s="16" t="n"/>
+      <c r="I305" s="14" t="n"/>
     </row>
     <row r="306" ht="18" customHeight="1">
-      <c r="I306" s="16" t="n"/>
+      <c r="I306" s="14" t="n"/>
     </row>
     <row r="307" ht="18" customHeight="1">
-      <c r="I307" s="16" t="n"/>
+      <c r="I307" s="14" t="n"/>
     </row>
     <row r="308" ht="18" customHeight="1">
-      <c r="I308" s="16" t="n"/>
+      <c r="I308" s="14" t="n"/>
     </row>
     <row r="309" ht="18" customHeight="1">
-      <c r="I309" s="16" t="n"/>
+      <c r="I309" s="14" t="n"/>
     </row>
     <row r="310" ht="18" customHeight="1">
-      <c r="I310" s="16" t="n"/>
+      <c r="I310" s="14" t="n"/>
     </row>
     <row r="311" ht="18" customHeight="1">
-      <c r="I311" s="16" t="n"/>
+      <c r="I311" s="14" t="n"/>
     </row>
     <row r="312" ht="18" customHeight="1">
-      <c r="I312" s="16" t="n"/>
+      <c r="I312" s="14" t="n"/>
     </row>
     <row r="313" ht="18" customHeight="1">
-      <c r="I313" s="16" t="n"/>
+      <c r="I313" s="14" t="n"/>
     </row>
     <row r="314" ht="18" customHeight="1">
-      <c r="I314" s="16" t="n"/>
+      <c r="I314" s="14" t="n"/>
     </row>
     <row r="315" ht="18" customHeight="1">
-      <c r="I315" s="16" t="n"/>
+      <c r="I315" s="14" t="n"/>
     </row>
     <row r="316" ht="18" customHeight="1">
-      <c r="I316" s="16" t="n"/>
+      <c r="I316" s="14" t="n"/>
     </row>
     <row r="317" ht="18" customHeight="1">
-      <c r="I317" s="16" t="n"/>
+      <c r="I317" s="14" t="n"/>
     </row>
     <row r="318" ht="18" customHeight="1">
-      <c r="I318" s="16" t="n"/>
+      <c r="I318" s="14" t="n"/>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="I319" s="16" t="n"/>
+      <c r="I319" s="14" t="n"/>
     </row>
     <row r="320" ht="18" customHeight="1">
-      <c r="I320" s="16" t="n"/>
+      <c r="I320" s="14" t="n"/>
     </row>
     <row r="321" ht="18" customHeight="1">
-      <c r="I321" s="16" t="n"/>
+      <c r="I321" s="14" t="n"/>
     </row>
     <row r="322" ht="18" customHeight="1">
-      <c r="I322" s="16" t="n"/>
+      <c r="I322" s="14" t="n"/>
     </row>
     <row r="323" ht="18" customHeight="1">
-      <c r="I323" s="16" t="n"/>
+      <c r="I323" s="14" t="n"/>
     </row>
     <row r="324" ht="18" customHeight="1">
-      <c r="I324" s="16" t="n"/>
+      <c r="I324" s="14" t="n"/>
     </row>
     <row r="325" ht="18" customHeight="1">
-      <c r="I325" s="16" t="n"/>
+      <c r="I325" s="14" t="n"/>
     </row>
     <row r="326" ht="18" customHeight="1">
-      <c r="I326" s="16" t="n"/>
+      <c r="I326" s="14" t="n"/>
     </row>
     <row r="327" ht="18" customHeight="1">
-      <c r="I327" s="16" t="n"/>
+      <c r="I327" s="14" t="n"/>
     </row>
     <row r="328" ht="18" customHeight="1">
-      <c r="I328" s="16" t="n"/>
+      <c r="I328" s="14" t="n"/>
     </row>
     <row r="329" ht="18" customHeight="1">
-      <c r="I329" s="16" t="n"/>
+      <c r="I329" s="14" t="n"/>
     </row>
     <row r="330" ht="18" customHeight="1">
-      <c r="I330" s="16" t="n"/>
+      <c r="I330" s="14" t="n"/>
     </row>
     <row r="331" ht="18" customHeight="1">
-      <c r="I331" s="16" t="n"/>
+      <c r="I331" s="14" t="n"/>
     </row>
     <row r="332" ht="18" customHeight="1">
-      <c r="I332" s="16" t="n"/>
+      <c r="I332" s="14" t="n"/>
     </row>
     <row r="333" ht="18" customHeight="1">
-      <c r="I333" s="16" t="n"/>
+      <c r="I333" s="14" t="n"/>
     </row>
     <row r="334" ht="18" customHeight="1">
-      <c r="I334" s="16" t="n"/>
+      <c r="I334" s="14" t="n"/>
     </row>
     <row r="335" ht="18" customHeight="1">
-      <c r="I335" s="16" t="n"/>
+      <c r="I335" s="14" t="n"/>
     </row>
     <row r="336" ht="18" customHeight="1">
-      <c r="I336" s="16" t="n"/>
+      <c r="I336" s="14" t="n"/>
     </row>
     <row r="337" ht="18" customHeight="1">
-      <c r="I337" s="16" t="n"/>
+      <c r="I337" s="14" t="n"/>
     </row>
     <row r="338" ht="18" customHeight="1">
-      <c r="I338" s="16" t="n"/>
+      <c r="I338" s="14" t="n"/>
     </row>
     <row r="339" ht="18" customHeight="1">
-      <c r="I339" s="16" t="n"/>
+      <c r="I339" s="14" t="n"/>
     </row>
     <row r="340" ht="18" customHeight="1">
-      <c r="I340" s="16" t="n"/>
+      <c r="I340" s="14" t="n"/>
     </row>
     <row r="341" ht="18" customHeight="1">
-      <c r="I341" s="16" t="n"/>
+      <c r="I341" s="14" t="n"/>
     </row>
     <row r="342" ht="18" customHeight="1">
-      <c r="I342" s="16" t="n"/>
+      <c r="I342" s="14" t="n"/>
     </row>
     <row r="343" ht="18" customHeight="1">
-      <c r="I343" s="16" t="n"/>
+      <c r="I343" s="14" t="n"/>
     </row>
     <row r="344" ht="18" customHeight="1">
-      <c r="I344" s="16" t="n"/>
+      <c r="I344" s="14" t="n"/>
     </row>
     <row r="345" ht="18" customHeight="1">
-      <c r="I345" s="16" t="n"/>
+      <c r="I345" s="14" t="n"/>
     </row>
     <row r="346" ht="18" customHeight="1">
-      <c r="I346" s="16" t="n"/>
+      <c r="I346" s="14" t="n"/>
     </row>
     <row r="347" ht="18" customHeight="1">
-      <c r="I347" s="16" t="n"/>
+      <c r="I347" s="14" t="n"/>
     </row>
     <row r="348" ht="18" customHeight="1">
-      <c r="I348" s="16" t="n"/>
+      <c r="I348" s="14" t="n"/>
     </row>
     <row r="349" ht="18" customHeight="1">
-      <c r="I349" s="16" t="n"/>
+      <c r="I349" s="14" t="n"/>
     </row>
     <row r="350" ht="18" customHeight="1">
-      <c r="I350" s="16" t="n"/>
+      <c r="I350" s="14" t="n"/>
     </row>
     <row r="351" ht="18" customHeight="1">
-      <c r="I351" s="16" t="n"/>
+      <c r="I351" s="14" t="n"/>
     </row>
     <row r="352" ht="18" customHeight="1">
-      <c r="I352" s="16" t="n"/>
+      <c r="I352" s="14" t="n"/>
     </row>
     <row r="353" ht="18" customHeight="1">
-      <c r="I353" s="16" t="n"/>
+      <c r="I353" s="14" t="n"/>
     </row>
     <row r="354" ht="18" customHeight="1">
-      <c r="I354" s="16" t="n"/>
+      <c r="I354" s="14" t="n"/>
     </row>
     <row r="355" ht="18" customHeight="1">
-      <c r="I355" s="16" t="n"/>
+      <c r="I355" s="14" t="n"/>
     </row>
     <row r="356" ht="18" customHeight="1">
-      <c r="I356" s="16" t="n"/>
+      <c r="I356" s="14" t="n"/>
     </row>
     <row r="357" ht="18" customHeight="1">
-      <c r="I357" s="16" t="n"/>
+      <c r="I357" s="14" t="n"/>
     </row>
     <row r="358" ht="18" customHeight="1">
-      <c r="I358" s="16" t="n"/>
+      <c r="I358" s="14" t="n"/>
     </row>
     <row r="359" ht="18" customHeight="1">
-      <c r="I359" s="16" t="n"/>
+      <c r="I359" s="14" t="n"/>
     </row>
     <row r="360" ht="18" customHeight="1">
-      <c r="I360" s="16" t="n"/>
+      <c r="I360" s="14" t="n"/>
     </row>
     <row r="361" ht="18" customHeight="1">
-      <c r="I361" s="16" t="n"/>
+      <c r="I361" s="14" t="n"/>
     </row>
     <row r="362" ht="18" customHeight="1">
-      <c r="I362" s="16" t="n"/>
+      <c r="I362" s="14" t="n"/>
     </row>
     <row r="363" ht="18" customHeight="1">
-      <c r="I363" s="16" t="n"/>
+      <c r="I363" s="14" t="n"/>
     </row>
     <row r="364" ht="18" customHeight="1">
-      <c r="I364" s="16" t="n"/>
+      <c r="I364" s="14" t="n"/>
     </row>
     <row r="365" ht="18" customHeight="1">
-      <c r="I365" s="16" t="n"/>
+      <c r="I365" s="14" t="n"/>
     </row>
     <row r="366" ht="18" customHeight="1">
-      <c r="I366" s="16" t="n"/>
+      <c r="I366" s="14" t="n"/>
     </row>
     <row r="367" ht="18" customHeight="1">
-      <c r="I367" s="16" t="n"/>
+      <c r="I367" s="14" t="n"/>
     </row>
     <row r="368" ht="18" customHeight="1">
-      <c r="I368" s="16" t="n"/>
+      <c r="I368" s="14" t="n"/>
     </row>
     <row r="369" ht="18" customHeight="1">
-      <c r="I369" s="16" t="n"/>
+      <c r="I369" s="14" t="n"/>
     </row>
     <row r="370" ht="18" customHeight="1">
-      <c r="I370" s="16" t="n"/>
+      <c r="I370" s="14" t="n"/>
     </row>
     <row r="371" ht="18" customHeight="1">
-      <c r="I371" s="16" t="n"/>
+      <c r="I371" s="14" t="n"/>
     </row>
     <row r="372" ht="18" customHeight="1">
-      <c r="I372" s="16" t="n"/>
+      <c r="I372" s="14" t="n"/>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="I373" s="16" t="n"/>
+      <c r="I373" s="14" t="n"/>
     </row>
     <row r="374" ht="18" customHeight="1">
-      <c r="I374" s="16" t="n"/>
+      <c r="I374" s="14" t="n"/>
     </row>
     <row r="375" ht="18" customHeight="1">
-      <c r="I375" s="16" t="n"/>
+      <c r="I375" s="14" t="n"/>
     </row>
     <row r="376" ht="18" customHeight="1">
-      <c r="I376" s="16" t="n"/>
+      <c r="I376" s="14" t="n"/>
     </row>
     <row r="377" ht="18" customHeight="1">
-      <c r="I377" s="16" t="n"/>
+      <c r="I377" s="14" t="n"/>
     </row>
     <row r="378" ht="18" customHeight="1">
-      <c r="I378" s="16" t="n"/>
+      <c r="I378" s="14" t="n"/>
     </row>
     <row r="379" ht="18" customHeight="1">
-      <c r="I379" s="16" t="n"/>
+      <c r="I379" s="14" t="n"/>
     </row>
     <row r="380" ht="18" customHeight="1">
-      <c r="I380" s="16" t="n"/>
+      <c r="I380" s="14" t="n"/>
     </row>
     <row r="381" ht="18" customHeight="1">
-      <c r="I381" s="16" t="n"/>
+      <c r="I381" s="14" t="n"/>
     </row>
     <row r="382" ht="18" customHeight="1">
-      <c r="I382" s="16" t="n"/>
+      <c r="I382" s="14" t="n"/>
     </row>
     <row r="383" ht="18" customHeight="1">
-      <c r="I383" s="16" t="n"/>
+      <c r="I383" s="14" t="n"/>
     </row>
     <row r="384" ht="18" customHeight="1">
-      <c r="I384" s="16" t="n"/>
+      <c r="I384" s="14" t="n"/>
     </row>
     <row r="385" ht="18" customHeight="1">
-      <c r="I385" s="16" t="n"/>
+      <c r="I385" s="14" t="n"/>
     </row>
     <row r="386" ht="18" customHeight="1">
-      <c r="I386" s="16" t="n"/>
+      <c r="I386" s="14" t="n"/>
     </row>
     <row r="387" ht="18" customHeight="1">
-      <c r="I387" s="16" t="n"/>
+      <c r="I387" s="14" t="n"/>
     </row>
     <row r="388" ht="18" customHeight="1">
-      <c r="I388" s="16" t="n"/>
+      <c r="I388" s="14" t="n"/>
     </row>
     <row r="389" ht="18" customHeight="1">
-      <c r="I389" s="16" t="n"/>
+      <c r="I389" s="14" t="n"/>
     </row>
     <row r="390" ht="18" customHeight="1">
-      <c r="I390" s="16" t="n"/>
+      <c r="I390" s="14" t="n"/>
     </row>
     <row r="391" ht="18" customHeight="1">
-      <c r="I391" s="16" t="n"/>
+      <c r="I391" s="14" t="n"/>
     </row>
     <row r="392" ht="18" customHeight="1">
-      <c r="I392" s="16" t="n"/>
+      <c r="I392" s="14" t="n"/>
     </row>
     <row r="393" ht="18" customHeight="1">
-      <c r="I393" s="16" t="n"/>
+      <c r="I393" s="14" t="n"/>
     </row>
     <row r="394" ht="18" customHeight="1">
-      <c r="I394" s="16" t="n"/>
+      <c r="I394" s="14" t="n"/>
     </row>
     <row r="395" ht="18" customHeight="1">
-      <c r="I395" s="16" t="n"/>
+      <c r="I395" s="14" t="n"/>
     </row>
     <row r="396" ht="18" customHeight="1">
-      <c r="I396" s="16" t="n"/>
+      <c r="I396" s="14" t="n"/>
     </row>
     <row r="397" ht="18" customHeight="1">
-      <c r="I397" s="16" t="n"/>
+      <c r="I397" s="14" t="n"/>
     </row>
     <row r="398" ht="18" customHeight="1">
-      <c r="I398" s="16" t="n"/>
+      <c r="I398" s="14" t="n"/>
     </row>
     <row r="399" ht="18" customHeight="1">
-      <c r="I399" s="16" t="n"/>
+      <c r="I399" s="14" t="n"/>
     </row>
     <row r="400" ht="18" customHeight="1">
-      <c r="I400" s="16" t="n"/>
+      <c r="I400" s="14" t="n"/>
     </row>
     <row r="401" ht="18" customHeight="1">
-      <c r="I401" s="16" t="n"/>
+      <c r="I401" s="14" t="n"/>
     </row>
     <row r="402" ht="18" customHeight="1">
-      <c r="I402" s="16" t="n"/>
+      <c r="I402" s="14" t="n"/>
     </row>
     <row r="403" ht="18" customHeight="1">
-      <c r="I403" s="16" t="n"/>
+      <c r="I403" s="14" t="n"/>
     </row>
     <row r="404" ht="18" customHeight="1">
-      <c r="I404" s="16" t="n"/>
+      <c r="I404" s="14" t="n"/>
     </row>
     <row r="405" ht="18" customHeight="1">
-      <c r="I405" s="16" t="n"/>
+      <c r="I405" s="14" t="n"/>
     </row>
     <row r="406" ht="18" customHeight="1">
-      <c r="I406" s="16" t="n"/>
+      <c r="I406" s="14" t="n"/>
     </row>
     <row r="407" ht="18" customHeight="1">
-      <c r="I407" s="16" t="n"/>
+      <c r="I407" s="14" t="n"/>
     </row>
     <row r="408" ht="18" customHeight="1">
-      <c r="I408" s="16" t="n"/>
+      <c r="I408" s="14" t="n"/>
     </row>
     <row r="409" ht="18" customHeight="1">
-      <c r="I409" s="16" t="n"/>
+      <c r="I409" s="14" t="n"/>
     </row>
     <row r="410" ht="18" customHeight="1">
-      <c r="I410" s="16" t="n"/>
+      <c r="I410" s="14" t="n"/>
     </row>
     <row r="411" ht="18" customHeight="1">
-      <c r="I411" s="16" t="n"/>
+      <c r="I411" s="14" t="n"/>
     </row>
     <row r="412" ht="18" customHeight="1">
-      <c r="I412" s="16" t="n"/>
+      <c r="I412" s="14" t="n"/>
     </row>
     <row r="413" ht="18" customHeight="1">
-      <c r="I413" s="16" t="n"/>
+      <c r="I413" s="14" t="n"/>
     </row>
     <row r="414" ht="18" customHeight="1">
-      <c r="I414" s="16" t="n"/>
+      <c r="I414" s="14" t="n"/>
     </row>
     <row r="415" ht="18" customHeight="1">
-      <c r="I415" s="16" t="n"/>
+      <c r="I415" s="14" t="n"/>
     </row>
     <row r="416" ht="18" customHeight="1">
-      <c r="I416" s="16" t="n"/>
+      <c r="I416" s="14" t="n"/>
     </row>
     <row r="417" ht="18" customHeight="1">
-      <c r="I417" s="16" t="n"/>
+      <c r="I417" s="14" t="n"/>
     </row>
     <row r="418" ht="18" customHeight="1">
-      <c r="I418" s="16" t="n"/>
+      <c r="I418" s="14" t="n"/>
     </row>
     <row r="419" ht="18" customHeight="1">
-      <c r="I419" s="16" t="n"/>
+      <c r="I419" s="14" t="n"/>
     </row>
     <row r="420" ht="18" customHeight="1">
-      <c r="I420" s="16" t="n"/>
+      <c r="I420" s="14" t="n"/>
     </row>
     <row r="421" ht="18" customHeight="1">
-      <c r="I421" s="16" t="n"/>
+      <c r="I421" s="14" t="n"/>
     </row>
     <row r="422" ht="18" customHeight="1">
-      <c r="I422" s="16" t="n"/>
+      <c r="I422" s="14" t="n"/>
     </row>
     <row r="423" ht="18" customHeight="1">
-      <c r="I423" s="16" t="n"/>
+      <c r="I423" s="14" t="n"/>
     </row>
     <row r="424" ht="18" customHeight="1">
-      <c r="I424" s="16" t="n"/>
+      <c r="I424" s="14" t="n"/>
     </row>
     <row r="425" ht="18" customHeight="1">
-      <c r="I425" s="16" t="n"/>
+      <c r="I425" s="14" t="n"/>
     </row>
     <row r="426" ht="18" customHeight="1">
-      <c r="I426" s="16" t="n"/>
+      <c r="I426" s="14" t="n"/>
     </row>
     <row r="427" ht="18" customHeight="1">
-      <c r="I427" s="16" t="n"/>
+      <c r="I427" s="14" t="n"/>
     </row>
     <row r="428" ht="18" customHeight="1">
-      <c r="I428" s="16" t="n"/>
+      <c r="I428" s="14" t="n"/>
     </row>
     <row r="429" ht="18" customHeight="1">
-      <c r="I429" s="16" t="n"/>
+      <c r="I429" s="14" t="n"/>
     </row>
     <row r="430" ht="18" customHeight="1">
-      <c r="I430" s="16" t="n"/>
+      <c r="I430" s="14" t="n"/>
     </row>
     <row r="431" ht="18" customHeight="1">
-      <c r="I431" s="16" t="n"/>
+      <c r="I431" s="14" t="n"/>
     </row>
     <row r="432" ht="18" customHeight="1">
-      <c r="I432" s="16" t="n"/>
+      <c r="I432" s="14" t="n"/>
     </row>
     <row r="433" ht="18" customHeight="1">
-      <c r="I433" s="16" t="n"/>
+      <c r="I433" s="14" t="n"/>
     </row>
     <row r="434" ht="18" customHeight="1">
-      <c r="I434" s="16" t="n"/>
+      <c r="I434" s="14" t="n"/>
     </row>
     <row r="435" ht="18" customHeight="1">
-      <c r="I435" s="16" t="n"/>
+      <c r="I435" s="14" t="n"/>
     </row>
     <row r="436" ht="18" customHeight="1">
-      <c r="I436" s="16" t="n"/>
+      <c r="I436" s="14" t="n"/>
     </row>
     <row r="437" ht="18" customHeight="1">
-      <c r="I437" s="16" t="n"/>
+      <c r="I437" s="14" t="n"/>
     </row>
     <row r="438" ht="18" customHeight="1">
-      <c r="I438" s="16" t="n"/>
+      <c r="I438" s="14" t="n"/>
     </row>
     <row r="439" ht="18" customHeight="1">
-      <c r="I439" s="16" t="n"/>
+      <c r="I439" s="14" t="n"/>
     </row>
     <row r="440" ht="18" customHeight="1">
-      <c r="I440" s="16" t="n"/>
+      <c r="I440" s="14" t="n"/>
     </row>
     <row r="441" ht="18" customHeight="1">
-      <c r="I441" s="16" t="n"/>
+      <c r="I441" s="14" t="n"/>
     </row>
     <row r="442" ht="18" customHeight="1">
-      <c r="I442" s="16" t="n"/>
+      <c r="I442" s="14" t="n"/>
     </row>
     <row r="443" ht="18" customHeight="1">
-      <c r="I443" s="16" t="n"/>
+      <c r="I443" s="14" t="n"/>
     </row>
     <row r="444" ht="18" customHeight="1">
-      <c r="I444" s="16" t="n"/>
+      <c r="I444" s="14" t="n"/>
     </row>
     <row r="445" ht="18" customHeight="1">
-      <c r="I445" s="16" t="n"/>
+      <c r="I445" s="14" t="n"/>
     </row>
     <row r="446" ht="18" customHeight="1">
-      <c r="I446" s="16" t="n"/>
+      <c r="I446" s="14" t="n"/>
     </row>
     <row r="447" ht="18" customHeight="1">
-      <c r="I447" s="16" t="n"/>
+      <c r="I447" s="14" t="n"/>
     </row>
     <row r="448" ht="18" customHeight="1">
-      <c r="I448" s="16" t="n"/>
+      <c r="I448" s="14" t="n"/>
     </row>
     <row r="449" ht="18" customHeight="1">
-      <c r="I449" s="16" t="n"/>
+      <c r="I449" s="14" t="n"/>
     </row>
     <row r="450" ht="18" customHeight="1">
-      <c r="I450" s="16" t="n"/>
+      <c r="I450" s="14" t="n"/>
     </row>
     <row r="451" ht="18" customHeight="1">
-      <c r="I451" s="16" t="n"/>
+      <c r="I451" s="14" t="n"/>
     </row>
     <row r="452" ht="18" customHeight="1">
-      <c r="I452" s="16" t="n"/>
+      <c r="I452" s="14" t="n"/>
     </row>
     <row r="453" ht="18" customHeight="1">
-      <c r="I453" s="16" t="n"/>
+      <c r="I453" s="14" t="n"/>
     </row>
     <row r="454" ht="18" customHeight="1">
-      <c r="I454" s="16" t="n"/>
+      <c r="I454" s="14" t="n"/>
     </row>
     <row r="455" ht="18" customHeight="1">
-      <c r="I455" s="16" t="n"/>
+      <c r="I455" s="14" t="n"/>
     </row>
     <row r="456" ht="18" customHeight="1">
-      <c r="I456" s="16" t="n"/>
+      <c r="I456" s="14" t="n"/>
     </row>
     <row r="457" ht="18" customHeight="1">
-      <c r="I457" s="16" t="n"/>
+      <c r="I457" s="14" t="n"/>
     </row>
     <row r="458" ht="18" customHeight="1">
-      <c r="I458" s="16" t="n"/>
+      <c r="I458" s="14" t="n"/>
     </row>
     <row r="459" ht="18" customHeight="1">
-      <c r="I459" s="16" t="n"/>
+      <c r="I459" s="14" t="n"/>
     </row>
     <row r="460" ht="18" customHeight="1">
-      <c r="I460" s="16" t="n"/>
+      <c r="I460" s="14" t="n"/>
     </row>
     <row r="461" ht="18" customHeight="1">
-      <c r="I461" s="16" t="n"/>
+      <c r="I461" s="14" t="n"/>
     </row>
     <row r="462" ht="18" customHeight="1">
-      <c r="I462" s="16" t="n"/>
+      <c r="I462" s="14" t="n"/>
     </row>
     <row r="463" ht="18" customHeight="1">
-      <c r="I463" s="16" t="n"/>
+      <c r="I463" s="14" t="n"/>
     </row>
     <row r="464" ht="18" customHeight="1">
-      <c r="I464" s="16" t="n"/>
+      <c r="I464" s="14" t="n"/>
     </row>
     <row r="465" ht="18" customHeight="1">
-      <c r="I465" s="16" t="n"/>
+      <c r="I465" s="14" t="n"/>
     </row>
     <row r="466" ht="18" customHeight="1">
-      <c r="I466" s="16" t="n"/>
+      <c r="I466" s="14" t="n"/>
     </row>
     <row r="467" ht="18" customHeight="1">
-      <c r="I467" s="16" t="n"/>
+      <c r="I467" s="14" t="n"/>
     </row>
     <row r="468" ht="18" customHeight="1">
-      <c r="I468" s="16" t="n"/>
+      <c r="I468" s="14" t="n"/>
     </row>
     <row r="469" ht="18" customHeight="1">
-      <c r="I469" s="16" t="n"/>
+      <c r="I469" s="14" t="n"/>
     </row>
     <row r="470" ht="18" customHeight="1">
-      <c r="I470" s="16" t="n"/>
+      <c r="I470" s="14" t="n"/>
     </row>
     <row r="471" ht="18" customHeight="1">
-      <c r="I471" s="16" t="n"/>
+      <c r="I471" s="14" t="n"/>
     </row>
     <row r="472" ht="18" customHeight="1">
-      <c r="I472" s="16" t="n"/>
+      <c r="I472" s="14" t="n"/>
     </row>
     <row r="473" ht="18" customHeight="1">
-      <c r="I473" s="16" t="n"/>
+      <c r="I473" s="14" t="n"/>
     </row>
     <row r="474" ht="18" customHeight="1">
-      <c r="I474" s="16" t="n"/>
+      <c r="I474" s="14" t="n"/>
     </row>
     <row r="475" ht="18" customHeight="1">
-      <c r="I475" s="16" t="n"/>
+      <c r="I475" s="14" t="n"/>
     </row>
     <row r="476" ht="18" customHeight="1">
-      <c r="I476" s="16" t="n"/>
+      <c r="I476" s="14" t="n"/>
     </row>
     <row r="477" ht="18" customHeight="1">
-      <c r="I477" s="16" t="n"/>
+      <c r="I477" s="14" t="n"/>
     </row>
     <row r="478" ht="18" customHeight="1">
-      <c r="I478" s="16" t="n"/>
+      <c r="I478" s="14" t="n"/>
     </row>
     <row r="479" ht="18" customHeight="1">
-      <c r="I479" s="16" t="n"/>
+      <c r="I479" s="14" t="n"/>
     </row>
     <row r="480" ht="18" customHeight="1">
-      <c r="I480" s="16" t="n"/>
+      <c r="I480" s="14" t="n"/>
     </row>
     <row r="481" ht="18" customHeight="1">
-      <c r="I481" s="16" t="n"/>
+      <c r="I481" s="14" t="n"/>
     </row>
     <row r="482" ht="18" customHeight="1">
-      <c r="I482" s="16" t="n"/>
+      <c r="I482" s="14" t="n"/>
     </row>
     <row r="483" ht="18" customHeight="1">
-      <c r="I483" s="16" t="n"/>
+      <c r="I483" s="14" t="n"/>
     </row>
     <row r="484" ht="18" customHeight="1">
-      <c r="I484" s="16" t="n"/>
+      <c r="I484" s="14" t="n"/>
     </row>
     <row r="485" ht="18" customHeight="1">
-      <c r="I485" s="16" t="n"/>
+      <c r="I485" s="14" t="n"/>
     </row>
     <row r="486" ht="18" customHeight="1">
-      <c r="I486" s="16" t="n"/>
+      <c r="I486" s="14" t="n"/>
     </row>
     <row r="487" ht="18" customHeight="1">
-      <c r="I487" s="16" t="n"/>
+      <c r="I487" s="14" t="n"/>
     </row>
     <row r="488" ht="18" customHeight="1">
-      <c r="I488" s="16" t="n"/>
+      <c r="I488" s="14" t="n"/>
     </row>
     <row r="489" ht="18" customHeight="1">
-      <c r="I489" s="16" t="n"/>
+      <c r="I489" s="14" t="n"/>
     </row>
     <row r="490" ht="18" customHeight="1">
-      <c r="I490" s="16" t="n"/>
+      <c r="I490" s="14" t="n"/>
     </row>
     <row r="491" ht="18" customHeight="1">
-      <c r="I491" s="16" t="n"/>
+      <c r="I491" s="14" t="n"/>
     </row>
     <row r="492" ht="18" customHeight="1">
-      <c r="I492" s="16" t="n"/>
+      <c r="I492" s="14" t="n"/>
     </row>
     <row r="493" ht="18" customHeight="1">
-      <c r="I493" s="16" t="n"/>
+      <c r="I493" s="14" t="n"/>
     </row>
     <row r="494" ht="18" customHeight="1">
-      <c r="I494" s="16" t="n"/>
+      <c r="I494" s="14" t="n"/>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="I495" s="16" t="n"/>
+      <c r="I495" s="14" t="n"/>
     </row>
     <row r="496" ht="18" customHeight="1">
-      <c r="I496" s="16" t="n"/>
+      <c r="I496" s="14" t="n"/>
     </row>
     <row r="497" ht="18" customHeight="1">
-      <c r="I497" s="16" t="n"/>
+      <c r="I497" s="14" t="n"/>
     </row>
     <row r="498" ht="18" customHeight="1">
-      <c r="I498" s="16" t="n"/>
+      <c r="I498" s="14" t="n"/>
     </row>
     <row r="499" ht="18" customHeight="1">
-      <c r="I499" s="16" t="n"/>
+      <c r="I499" s="14" t="n"/>
     </row>
     <row r="500" ht="18" customHeight="1">
-      <c r="I500" s="16" t="n"/>
+      <c r="I500" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5609,8 +5551,8 @@
     <mergeCell ref="E1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, otros — o dejar vacío (pago normal)." type="list">
-      <formula1>"reclamo,compromiso,otros"</formula1>
+    <dataValidation sqref="K4:K500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="CATEGORIA inválida" error="Valores: reclamo, compromiso, exoneracion, otros — o dejar vacío (pago normal)." type="list">
+      <formula1>"reclamo,compromiso,exoneracion,otros"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
